--- a/Luban/Excel/CombatBuff.xlsx
+++ b/Luban/Excel/CombatBuff.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\Return0\Luban\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B2CEE81-6149-438E-909D-D91D83DFD445}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0440AD3-AB4E-4719-88E9-C1376E3CBC36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -300,6 +300,18 @@
     <t>回避</t>
   </si>
   <si>
+    <t>1/2/3层提供50/75/100（与盲目状态的效果取最高值）</t>
+  </si>
+  <si>
+    <t>NumericParams,13070,FORMULA_71002,19</t>
+  </si>
+  <si>
+    <t>3,2</t>
+  </si>
+  <si>
+    <t>护体</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="10"/>
@@ -308,7 +320,81 @@
         <family val="2"/>
         <charset val="134"/>
       </rPr>
-      <t>至少减少受到的</t>
+      <t>等量抵免</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="9" tint="-0.499984740745262"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>杀式</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>造成的直接伤害</t>
+    </r>
+  </si>
+  <si>
+    <t>抵免等量层数的攻击造成的直接伤害（优先计算于防、破前）</t>
+  </si>
+  <si>
+    <t>ShieldAmount,1</t>
+  </si>
+  <si>
+    <t>3,2|5,6</t>
+  </si>
+  <si>
+    <t>反击</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF00B050"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>受到攻击后</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>自身未存在行动则消耗一层</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF92D050"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>反击</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>状态对其使用</t>
     </r>
     <r>
       <rPr>
@@ -318,6 +404,179 @@
         <family val="2"/>
         <charset val="134"/>
       </rPr>
+      <t>武杀式：反击</t>
+    </r>
+  </si>
+  <si>
+    <t>迅速</t>
+  </si>
+  <si>
+    <t>每层使行动加快{[int]}息</t>
+  </si>
+  <si>
+    <t>每层使行动加快1息</t>
+  </si>
+  <si>
+    <t>ActNodeInt,1</t>
+  </si>
+  <si>
+    <t>3,8</t>
+  </si>
+  <si>
+    <t>刚聚</t>
+  </si>
+  <si>
+    <t>每层使获得的刚炁增加1</t>
+  </si>
+  <si>
+    <t>GangQiUpInt,1</t>
+  </si>
+  <si>
+    <t>3,1</t>
+  </si>
+  <si>
+    <t>玄聚</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>每层使获得的</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>玄炁</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>增加{[int]}</t>
+    </r>
+  </si>
+  <si>
+    <t>每层使获得的玄炁增加1</t>
+  </si>
+  <si>
+    <t>XuanQiUpInt,1</t>
+  </si>
+  <si>
+    <t>力增</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>每层使</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>力</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>增加{[int]}</t>
+    </r>
+  </si>
+  <si>
+    <t>每层使力增加10%</t>
+  </si>
+  <si>
+    <t>STRPct,10</t>
+  </si>
+  <si>
+    <t>技增</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>每层使</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>技</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>增加{[int]}</t>
+    </r>
+  </si>
+  <si>
+    <t>每层使技增加10%</t>
+  </si>
+  <si>
+    <t>INTPct,10</t>
+  </si>
+  <si>
+    <t>武增</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>每层使</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
       <t>武杀式</t>
     </r>
     <r>
@@ -328,7 +587,78 @@
         <family val="2"/>
         <charset val="134"/>
       </rPr>
-      <t>{[int]}%</t>
+      <t>威力增加5百分比</t>
+    </r>
+  </si>
+  <si>
+    <t>150%→155%</t>
+  </si>
+  <si>
+    <t>MartialCoefficientInt,5</t>
+  </si>
+  <si>
+    <t>术增</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>每层使</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>术杀式</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>威力增加5百分比</t>
+    </r>
+  </si>
+  <si>
+    <t>ArcaneCoefficientInt,5</t>
+  </si>
+  <si>
+    <t>巧增</t>
+  </si>
+  <si>
+    <t>每层使巧增加{[int]}</t>
+  </si>
+  <si>
+    <t>每层使巧增加10%</t>
+  </si>
+  <si>
+    <t>DEXPct,10</t>
+  </si>
+  <si>
+    <t>藏身</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>抵免{[int]}次敌手</t>
     </r>
     <r>
       <rPr>
@@ -338,7 +668,7 @@
         <family val="2"/>
         <charset val="134"/>
       </rPr>
-      <t>敌手的力</t>
+      <t>武杀式</t>
     </r>
     <r>
       <rPr>
@@ -348,7 +678,45 @@
         <family val="2"/>
         <charset val="134"/>
       </rPr>
-      <t>的直接伤害，至少减少行动目标对自身的</t>
+      <t>、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="9" tint="0.39997558519241921"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>技御式</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>带来的异常状态，防增加30+GR*3</t>
+    </r>
+  </si>
+  <si>
+    <t>6,1</t>
+  </si>
+  <si>
+    <t>隐魂</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>抵免{[int]}次敌手</t>
     </r>
     <r>
       <rPr>
@@ -368,17 +736,17 @@
         <family val="2"/>
         <charset val="134"/>
       </rPr>
-      <t>伤害{[int]}%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF00B0F0"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>敌手的技</t>
+      <t>、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="7" tint="0.39997558519241921"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>法咒式</t>
     </r>
     <r>
       <rPr>
@@ -388,22 +756,23 @@
         <family val="2"/>
         <charset val="134"/>
       </rPr>
-      <t>的直接伤害</t>
-    </r>
-  </si>
-  <si>
-    <t>1/2/3层提供50/75/100（与盲目状态的效果取最高值）</t>
-  </si>
-  <si>
-    <t>NumericParams,13070,FORMULA_71002,19</t>
-  </si>
-  <si>
-    <t>3,2</t>
-  </si>
-  <si>
-    <t>护体</t>
-  </si>
-  <si>
+      <t>带来的异常状态，破增加30+GR*3</t>
+    </r>
+  </si>
+  <si>
+    <t>雷行</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>武杀式</t>
+    </r>
     <r>
       <rPr>
         <sz val="10"/>
@@ -412,507 +781,11 @@
         <family val="2"/>
         <charset val="134"/>
       </rPr>
-      <t>等量抵免</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="9" tint="-0.499984740745262"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>杀式</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>造成的直接伤害</t>
-    </r>
-  </si>
-  <si>
-    <t>抵免等量层数的攻击造成的直接伤害（优先计算于防、破前）</t>
-  </si>
-  <si>
-    <t>ShieldAmount,1</t>
-  </si>
-  <si>
-    <t>3,2|5,6</t>
-  </si>
-  <si>
-    <t>反击</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF00B050"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>受到攻击后</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>自身未存在行动则消耗一层</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF92D050"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>反击</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>状态对其使用</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>武杀式：反击</t>
-    </r>
-  </si>
-  <si>
-    <t>迅速</t>
-  </si>
-  <si>
-    <t>每层使行动加快{[int]}息</t>
-  </si>
-  <si>
-    <t>每层使行动加快1息</t>
-  </si>
-  <si>
-    <t>ActNodeInt,1</t>
-  </si>
-  <si>
-    <t>3,8</t>
-  </si>
-  <si>
-    <t>刚聚</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>每层使获得的</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FFFFFF00"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>刚炁</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>增加{[int]}</t>
-    </r>
-  </si>
-  <si>
-    <t>每层使获得的刚炁增加1</t>
-  </si>
-  <si>
-    <t>GangQiUpInt,1</t>
-  </si>
-  <si>
-    <t>3,1</t>
-  </si>
-  <si>
-    <t>玄聚</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>每层使获得的</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF00B0F0"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>玄炁</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>增加{[int]}</t>
-    </r>
-  </si>
-  <si>
-    <t>每层使获得的玄炁增加1</t>
-  </si>
-  <si>
-    <t>XuanQiUpInt,1</t>
-  </si>
-  <si>
-    <t>力增</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>每层使</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>力</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>增加{[int]}</t>
-    </r>
-  </si>
-  <si>
-    <t>每层使力增加10%</t>
-  </si>
-  <si>
-    <t>STRPct,10</t>
-  </si>
-  <si>
-    <t>技增</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>每层使</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF00B0F0"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>技</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>增加{[int]}</t>
-    </r>
-  </si>
-  <si>
-    <t>每层使技增加10%</t>
-  </si>
-  <si>
-    <t>INTPct,10</t>
-  </si>
-  <si>
-    <t>武增</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>每层使</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>武杀式</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>威力增加5百分比</t>
-    </r>
-  </si>
-  <si>
-    <t>150%→155%</t>
-  </si>
-  <si>
-    <t>MartialCoefficientInt,5</t>
-  </si>
-  <si>
-    <t>术增</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>每层使</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF00B0F0"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>术杀式</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>威力增加5百分比</t>
-    </r>
-  </si>
-  <si>
-    <t>ArcaneCoefficientInt,5</t>
-  </si>
-  <si>
-    <t>巧增</t>
-  </si>
-  <si>
-    <t>每层使巧增加{[int]}</t>
-  </si>
-  <si>
-    <t>每层使巧增加10%</t>
-  </si>
-  <si>
-    <t>DEXPct,10</t>
-  </si>
-  <si>
-    <t>藏身</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>抵免{[int]}次敌手</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>武杀式</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>、</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="9" tint="0.39997558519241921"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>技御式</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>带来的异常状态，防增加30+GR*3</t>
-    </r>
-  </si>
-  <si>
-    <t>6,1</t>
-  </si>
-  <si>
-    <t>隐魂</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>抵免{[int]}次敌手</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF00B0F0"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>术杀式</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>、</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="7" tint="0.39997558519241921"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>法咒式</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>带来的异常状态，破增加30+GR*3</t>
-    </r>
-  </si>
-  <si>
-    <t>雷行</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>武杀式</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
       <t>直接造成伤害时根据行动加快效果提升伤害共{[int]}%，行动加快{[int]}息</t>
     </r>
   </si>
   <si>
     <t>行动每加快1息伤害提升5%，每层使行动加快1息</t>
-  </si>
-  <si>
-    <t>血炁甲</t>
   </si>
   <si>
     <r>
@@ -2904,6 +2777,122 @@
   </si>
   <si>
     <t>StackDecrement</t>
+    <phoneticPr fontId="21" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>至少减少受到的</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>武杀式</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>{[int]}%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>敌手的力</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>的直接伤害，至少减少行动目标对自身的</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>术杀式</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>伤害{[int]}%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>敌手的技</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>的直接伤害</t>
+    </r>
+    <phoneticPr fontId="21" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>每层使获得的</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFFFFF00"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>刚炁</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>增加{[int]}</t>
+    </r>
+    <phoneticPr fontId="21" type="noConversion"/>
+  </si>
+  <si>
+    <t>血炁甲</t>
     <phoneticPr fontId="21" type="noConversion"/>
   </si>
 </sst>
@@ -3450,12 +3439,12 @@
     <col min="1" max="3" width="9" style="1"/>
     <col min="4" max="4" width="16.125" style="1" customWidth="1"/>
     <col min="5" max="5" width="11.5" style="1" customWidth="1"/>
-    <col min="6" max="6" width="61.125" style="1" customWidth="1"/>
-    <col min="7" max="8" width="7.625" style="1" customWidth="1"/>
-    <col min="9" max="9" width="45.25" style="1" customWidth="1"/>
-    <col min="10" max="10" width="14.125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="137.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="76.75" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.625" style="1" customWidth="1"/>
+    <col min="9" max="10" width="14.125" style="1" customWidth="1"/>
     <col min="11" max="11" width="9" style="1"/>
-    <col min="12" max="12" width="9.625" style="1" customWidth="1"/>
+    <col min="12" max="12" width="15.625" style="1" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="8.375" style="1" customWidth="1"/>
     <col min="14" max="14" width="10.375" style="1" customWidth="1"/>
     <col min="15" max="15" width="15.125" style="1" customWidth="1"/>
@@ -3544,7 +3533,7 @@
         <v>23</v>
       </c>
       <c r="L2" s="6" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="M2" s="6" t="s">
         <v>24</v>
@@ -3593,7 +3582,7 @@
         <v>30</v>
       </c>
       <c r="M3" s="6" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="N3" s="6" t="s">
         <v>29</v>
@@ -3660,19 +3649,19 @@
         <v>36</v>
       </c>
       <c r="F5" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="G5" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="G5" s="1" t="s">
+      <c r="I5" s="1" t="s">
         <v>38</v>
-      </c>
-      <c r="I5" s="1" t="s">
-        <v>39</v>
       </c>
       <c r="K5" s="1">
         <v>3</v>
       </c>
       <c r="L5" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="M5" s="1">
         <v>1</v>
@@ -3695,22 +3684,22 @@
         <v>1</v>
       </c>
       <c r="D6" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="F6" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="F6" s="1" t="s">
+      <c r="G6" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="G6" s="1" t="s">
+      <c r="J6" s="1" t="s">
         <v>43</v>
-      </c>
-      <c r="J6" s="1" t="s">
-        <v>44</v>
       </c>
       <c r="K6" s="1">
         <v>-1</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="M6" s="1">
         <v>1</v>
@@ -3733,16 +3722,16 @@
         <v>1</v>
       </c>
       <c r="D7" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="F7" s="7" t="s">
         <v>46</v>
-      </c>
-      <c r="F7" s="7" t="s">
-        <v>47</v>
       </c>
       <c r="K7" s="1">
         <v>99</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="M7" s="1">
         <v>1</v>
@@ -3765,22 +3754,22 @@
         <v>1</v>
       </c>
       <c r="D8" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="F8" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="F8" s="1" t="s">
+      <c r="G8" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="G8" s="1" t="s">
+      <c r="J8" s="1" t="s">
         <v>50</v>
-      </c>
-      <c r="J8" s="1" t="s">
-        <v>51</v>
       </c>
       <c r="K8" s="1">
         <v>10</v>
       </c>
       <c r="L8" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="M8" s="1">
         <v>1</v>
@@ -3803,22 +3792,22 @@
         <v>1</v>
       </c>
       <c r="D9" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>360</v>
+      </c>
+      <c r="G9" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="F9" s="1" t="s">
+      <c r="J9" s="1" t="s">
         <v>54</v>
-      </c>
-      <c r="G9" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="J9" s="1" t="s">
-        <v>56</v>
       </c>
       <c r="K9" s="1">
         <v>5</v>
       </c>
       <c r="L9" s="1" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="M9" s="1">
         <v>1</v>
@@ -3841,22 +3830,22 @@
         <v>1</v>
       </c>
       <c r="D10" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="G10" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="F10" s="1" t="s">
+      <c r="J10" s="1" t="s">
         <v>59</v>
-      </c>
-      <c r="G10" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="J10" s="1" t="s">
-        <v>61</v>
       </c>
       <c r="K10" s="1">
         <v>5</v>
       </c>
       <c r="L10" s="1" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="M10" s="1">
         <v>1</v>
@@ -3879,22 +3868,22 @@
         <v>1</v>
       </c>
       <c r="D11" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="F11" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="G11" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="F11" s="8" t="s">
+      <c r="J11" s="1" t="s">
         <v>63</v>
-      </c>
-      <c r="G11" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="J11" s="1" t="s">
-        <v>65</v>
       </c>
       <c r="K11" s="1">
         <v>5</v>
       </c>
       <c r="L11" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="M11" s="1">
         <v>1</v>
@@ -3917,22 +3906,22 @@
         <v>1</v>
       </c>
       <c r="D12" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="F12" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="G12" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="F12" s="8" t="s">
+      <c r="J12" s="1" t="s">
         <v>67</v>
-      </c>
-      <c r="G12" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="J12" s="1" t="s">
-        <v>69</v>
       </c>
       <c r="K12" s="1">
         <v>5</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="M12" s="1">
         <v>1</v>
@@ -3955,22 +3944,22 @@
         <v>1</v>
       </c>
       <c r="D13" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="G13" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="F13" s="1" t="s">
+      <c r="J13" s="1" t="s">
         <v>71</v>
-      </c>
-      <c r="G13" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="J13" s="1" t="s">
-        <v>73</v>
       </c>
       <c r="K13" s="1">
         <v>5</v>
       </c>
       <c r="L13" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="M13" s="1">
         <v>1</v>
@@ -3993,19 +3982,19 @@
         <v>1</v>
       </c>
       <c r="D14" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="J14" s="1" t="s">
         <v>74</v>
-      </c>
-      <c r="F14" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="J14" s="1" t="s">
-        <v>76</v>
       </c>
       <c r="K14" s="1">
         <v>5</v>
       </c>
       <c r="L14" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="M14" s="1">
         <v>1</v>
@@ -4028,22 +4017,22 @@
         <v>1</v>
       </c>
       <c r="D15" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="G15" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="F15" s="1" t="s">
+      <c r="J15" s="1" t="s">
         <v>78</v>
-      </c>
-      <c r="G15" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="J15" s="1" t="s">
-        <v>80</v>
       </c>
       <c r="K15" s="1">
         <v>5</v>
       </c>
       <c r="L15" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="M15" s="1">
         <v>1</v>
@@ -4063,16 +4052,16 @@
         <v>1</v>
       </c>
       <c r="D16" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="K16" s="1">
+        <v>1</v>
+      </c>
+      <c r="L16" s="1" t="s">
         <v>81</v>
-      </c>
-      <c r="F16" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="K16" s="1">
-        <v>1</v>
-      </c>
-      <c r="L16" s="1" t="s">
-        <v>83</v>
       </c>
       <c r="M16" s="1">
         <v>2</v>
@@ -4095,16 +4084,16 @@
         <v>1</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="K17" s="1">
         <v>1</v>
       </c>
       <c r="L17" s="1" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="M17" s="1">
         <v>2</v>
@@ -4127,13 +4116,13 @@
         <v>1</v>
       </c>
       <c r="D18" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="F18" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="G18" s="1" t="s">
         <v>86</v>
-      </c>
-      <c r="F18" s="9" t="s">
-        <v>87</v>
-      </c>
-      <c r="G18" s="1" t="s">
-        <v>88</v>
       </c>
       <c r="K18" s="1">
         <v>5</v>
@@ -4162,19 +4151,19 @@
         <v>1</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>89</v>
+        <v>361</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="K19" s="1">
         <v>-1</v>
       </c>
       <c r="L19" s="1" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="M19" s="1">
         <v>1</v>
@@ -4197,10 +4186,10 @@
         <v>1</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="K20" s="1">
         <v>-1</v>
@@ -4229,16 +4218,16 @@
         <v>1</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="K21" s="1">
         <v>1</v>
       </c>
       <c r="L21" s="1" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="M21" s="1">
         <v>2</v>
@@ -4261,16 +4250,16 @@
         <v>1</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="K22" s="1">
         <v>-1</v>
       </c>
       <c r="L22" s="1" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="M22" s="1">
         <v>2</v>
@@ -4293,10 +4282,10 @@
         <v>1</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="K23" s="1">
         <v>10</v>
@@ -4325,10 +4314,10 @@
         <v>1</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="K24" s="1">
         <v>1</v>
@@ -4357,10 +4346,10 @@
         <v>1</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="K25" s="1">
         <v>1</v>
@@ -4389,19 +4378,19 @@
         <v>1</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="K26" s="1">
         <v>3</v>
       </c>
       <c r="L26" s="1" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="M26" s="1">
         <v>2</v>
@@ -4418,10 +4407,10 @@
         <v>1</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="K27" s="1">
         <v>99</v>
@@ -4444,19 +4433,19 @@
         <v>2</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="K29" s="1">
         <v>10</v>
       </c>
       <c r="L29" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="M29" s="1">
         <v>1</v>
@@ -4479,19 +4468,19 @@
         <v>2</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="K30" s="1">
         <v>8</v>
       </c>
       <c r="L30" s="1" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="M30" s="1">
         <v>2</v>
@@ -4514,10 +4503,10 @@
         <v>2</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="K31" s="1">
         <v>-1</v>
@@ -4546,10 +4535,10 @@
         <v>2</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="K32" s="1">
         <v>-1</v>
@@ -4578,10 +4567,10 @@
         <v>2</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="K33" s="1">
         <v>-1</v>
@@ -4610,10 +4599,10 @@
         <v>2</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="K34" s="1">
         <v>-1</v>
@@ -4642,16 +4631,16 @@
         <v>2</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="K35" s="1">
         <v>-1</v>
       </c>
       <c r="L35" s="1" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="M35" s="1">
         <v>2</v>
@@ -4674,19 +4663,19 @@
         <v>2</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="K36" s="1">
         <v>-1</v>
       </c>
       <c r="L36" s="1" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="M36" s="1">
         <v>1</v>
@@ -4709,19 +4698,19 @@
         <v>2</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="K37" s="1">
         <v>5</v>
       </c>
       <c r="L37" s="1" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="M37" s="1">
         <v>1</v>
@@ -4744,19 +4733,19 @@
         <v>2</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="K38" s="1">
         <v>5</v>
       </c>
       <c r="L38" s="1" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="M38" s="1">
         <v>1</v>
@@ -4779,19 +4768,19 @@
         <v>2</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="F39" s="8" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="K39" s="1">
         <v>5</v>
       </c>
       <c r="L39" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="M39" s="1">
         <v>1</v>
@@ -4814,19 +4803,19 @@
         <v>2</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="F40" s="8" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="G40" s="1" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="K40" s="1">
         <v>5</v>
       </c>
       <c r="L40" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="M40" s="1">
         <v>1</v>
@@ -4849,22 +4838,22 @@
         <v>2</v>
       </c>
       <c r="D41" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="F41" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="G41" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="J41" s="1" t="s">
         <v>143</v>
-      </c>
-      <c r="F41" s="8" t="s">
-        <v>144</v>
-      </c>
-      <c r="G41" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="J41" s="1" t="s">
-        <v>146</v>
       </c>
       <c r="K41" s="1">
         <v>5</v>
       </c>
       <c r="L41" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="M41" s="1">
         <v>1</v>
@@ -4887,22 +4876,22 @@
         <v>2</v>
       </c>
       <c r="D42" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="F42" s="8" t="s">
+        <v>145</v>
+      </c>
+      <c r="G42" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="J42" s="1" t="s">
         <v>147</v>
-      </c>
-      <c r="F42" s="8" t="s">
-        <v>148</v>
-      </c>
-      <c r="G42" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="J42" s="1" t="s">
-        <v>150</v>
       </c>
       <c r="K42" s="1">
         <v>5</v>
       </c>
       <c r="L42" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="M42" s="1">
         <v>1</v>
@@ -4925,16 +4914,16 @@
         <v>2</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="K43" s="1">
         <v>1</v>
       </c>
       <c r="L43" s="1" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="M43" s="1">
         <v>1</v>
@@ -4957,10 +4946,10 @@
         <v>2</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="K44" s="1">
         <v>2</v>
@@ -4989,19 +4978,19 @@
         <v>2</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="G45" s="1" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="K45" s="1">
         <v>3</v>
       </c>
       <c r="L45" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="M45" s="1">
         <v>1</v>
@@ -5024,10 +5013,10 @@
         <v>2</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="K46" s="1">
         <v>5</v>
@@ -5056,10 +5045,10 @@
         <v>2</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="K47" s="1">
         <v>5</v>
@@ -5088,10 +5077,10 @@
         <v>2</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="K48" s="1">
         <v>5</v>
@@ -5120,10 +5109,10 @@
         <v>2</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="K49" s="1">
         <v>5</v>
@@ -5152,10 +5141,10 @@
         <v>2</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="F50" s="7" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="K50" s="1">
         <v>10</v>
@@ -5181,10 +5170,10 @@
         <v>2</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="F51" s="7" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="K51" s="1">
         <v>-1</v>
@@ -5210,16 +5199,16 @@
         <v>2</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="F52" s="7" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="K52" s="1">
         <v>1</v>
       </c>
       <c r="L52" s="1" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="M52" s="1">
         <v>2</v>
@@ -5242,16 +5231,16 @@
         <v>2</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="F53" s="7" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="K53" s="1">
         <v>1</v>
       </c>
       <c r="L53" s="1" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="M53" s="1">
         <v>2</v>
@@ -5274,16 +5263,16 @@
         <v>2</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="F54" s="7" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="K54" s="1">
         <v>1</v>
       </c>
       <c r="L54" s="1" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="M54" s="1">
         <v>2</v>
@@ -5306,16 +5295,16 @@
         <v>2</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="F55" s="7" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="K55" s="1">
         <v>1</v>
       </c>
       <c r="L55" s="1" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="M55" s="1">
         <v>2</v>
@@ -5338,10 +5327,10 @@
         <v>2</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="K56" s="1">
         <v>-1</v>
@@ -5370,10 +5359,10 @@
         <v>2</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="G57" s="10">
         <v>1</v>
@@ -5384,7 +5373,7 @@
         <v>-1</v>
       </c>
       <c r="L57" s="1" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="M57" s="1">
         <v>2</v>
@@ -5407,13 +5396,13 @@
         <v>2</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="G58" s="1" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="K58" s="1">
         <v>5</v>
@@ -5442,13 +5431,13 @@
         <v>2</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="G59" s="1" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="K59" s="1">
         <v>5</v>
@@ -5477,10 +5466,10 @@
         <v>2</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="F60" s="8" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="K60" s="1">
         <v>1</v>
@@ -5509,16 +5498,16 @@
         <v>2</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="F61" s="8" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="K61" s="1">
         <v>1</v>
       </c>
       <c r="L61" s="1" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="M61" s="1">
         <v>2</v>
@@ -5541,16 +5530,16 @@
         <v>2</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="F62" s="7" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="K62" s="1">
         <v>10</v>
       </c>
       <c r="L62" s="1" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="M62" s="1">
         <v>1</v>
@@ -5573,10 +5562,10 @@
         <v>2</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="F63" s="8" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="K63" s="1">
         <v>-1</v>
@@ -5605,16 +5594,16 @@
         <v>3</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="F65" s="7" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="G65" s="1">
         <v>30</v>
       </c>
       <c r="L65" s="1" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="M65" s="1">
         <v>1</v>
@@ -5637,10 +5626,10 @@
         <v>3</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="K66" s="1">
         <v>1</v>
@@ -5669,16 +5658,16 @@
         <v>3</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="K67" s="1">
         <v>1</v>
       </c>
       <c r="L67" s="1" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="M67" s="1">
         <v>2</v>
@@ -5701,19 +5690,19 @@
         <v>3</v>
       </c>
       <c r="D68" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="F68" s="7" t="s">
+        <v>201</v>
+      </c>
+      <c r="G68" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="K68" s="1">
+        <v>1</v>
+      </c>
+      <c r="L68" s="1" t="s">
         <v>203</v>
-      </c>
-      <c r="F68" s="7" t="s">
-        <v>204</v>
-      </c>
-      <c r="G68" s="1" t="s">
-        <v>205</v>
-      </c>
-      <c r="K68" s="1">
-        <v>1</v>
-      </c>
-      <c r="L68" s="1" t="s">
-        <v>206</v>
       </c>
       <c r="M68" s="1">
         <v>2</v>
@@ -5736,16 +5725,16 @@
         <v>3</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="F69" s="8" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="G69" s="1" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="L69" s="1" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="M69" s="1">
         <v>1</v>
@@ -5768,16 +5757,16 @@
         <v>3</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="K70" s="1">
         <v>1</v>
       </c>
       <c r="L70" s="1" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="M70" s="1">
         <v>2</v>
@@ -5800,16 +5789,16 @@
         <v>3</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="F71" s="7" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="K71" s="1">
         <v>3</v>
       </c>
       <c r="L71" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="M71" s="1">
         <v>2</v>
@@ -5832,16 +5821,16 @@
         <v>3</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="F72" s="7" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="K72" s="1">
         <v>1</v>
       </c>
       <c r="L72" s="1" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="M72" s="1">
         <v>2</v>
@@ -5864,13 +5853,13 @@
         <v>3</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="F73" s="7" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="G73" s="1" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="N73" s="1">
         <v>3</v>
@@ -5890,10 +5879,10 @@
         <v>3</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="F74" s="9" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="N74" s="1">
         <v>9</v>
@@ -5913,16 +5902,16 @@
         <v>3</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="F75" s="7" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="K75" s="1">
         <v>1</v>
       </c>
       <c r="L75" s="1" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="M75" s="1">
         <v>2</v>
@@ -5945,16 +5934,16 @@
         <v>3</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="F76" s="7" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="K76" s="1">
         <v>1</v>
       </c>
       <c r="L76" s="1" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="M76" s="1">
         <v>2</v>
@@ -5977,16 +5966,16 @@
         <v>3</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="F77" s="7" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="K77" s="1">
         <v>1</v>
       </c>
       <c r="L77" s="1" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="M77" s="1">
         <v>2</v>
@@ -6009,16 +5998,16 @@
         <v>3</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="F78" s="7" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="K78" s="1">
         <v>1</v>
       </c>
       <c r="L78" s="1" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="M78" s="1">
         <v>2</v>
@@ -6041,16 +6030,16 @@
         <v>3</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="F79" s="7" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="K79" s="1">
         <v>1</v>
       </c>
       <c r="L79" s="1" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="M79" s="1">
         <v>2</v>
@@ -6073,16 +6062,16 @@
         <v>3</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="F80" s="7" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="K80" s="1">
         <v>1</v>
       </c>
       <c r="L80" s="1" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="M80" s="1">
         <v>2</v>
@@ -6105,16 +6094,16 @@
         <v>3</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="F81" s="7" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="K81" s="1">
         <v>1</v>
       </c>
       <c r="L81" s="1" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="M81" s="1">
         <v>2</v>
@@ -6137,16 +6126,16 @@
         <v>3</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="F82" s="7" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="K82" s="1">
         <v>1</v>
       </c>
       <c r="L82" s="1" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="M82" s="1">
         <v>2</v>
@@ -6169,16 +6158,16 @@
         <v>3</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="F83" s="7" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="K83" s="1">
         <v>1</v>
       </c>
       <c r="L83" s="1" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="M83" s="1">
         <v>2</v>
@@ -6201,16 +6190,16 @@
         <v>3</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="F84" s="7" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="K84" s="1">
         <v>1</v>
       </c>
       <c r="L84" s="1" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="M84" s="1">
         <v>2</v>
@@ -6233,16 +6222,16 @@
         <v>3</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="F85" s="7" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="K85" s="1">
         <v>1</v>
       </c>
       <c r="L85" s="1" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="M85" s="1">
         <v>2</v>
@@ -6265,16 +6254,16 @@
         <v>3</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="F86" s="7" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="K86" s="1">
         <v>1</v>
       </c>
       <c r="L86" s="1" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="M86" s="1">
         <v>2</v>
@@ -6297,16 +6286,16 @@
         <v>3</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="F87" s="7" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="K87" s="1">
         <v>1</v>
       </c>
       <c r="L87" s="1" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="M87" s="1">
         <v>2</v>
@@ -6329,16 +6318,16 @@
         <v>3</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="F88" s="7" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="K88" s="1">
         <v>1</v>
       </c>
       <c r="L88" s="1" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="M88" s="1">
         <v>2</v>
@@ -6361,16 +6350,16 @@
         <v>3</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="F89" s="7" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="K89" s="1">
         <v>1</v>
       </c>
       <c r="L89" s="1" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="M89" s="1">
         <v>2</v>
@@ -6393,16 +6382,16 @@
         <v>3</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="F90" s="7" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="K90" s="1">
         <v>1</v>
       </c>
       <c r="L90" s="1" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="M90" s="1">
         <v>2</v>
@@ -6425,13 +6414,13 @@
         <v>3</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="F91" s="9" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="G91" s="1" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="K91" s="1">
         <v>1</v>
@@ -6454,10 +6443,10 @@
         <v>3</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="F92" s="1" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="N92" s="1">
         <v>1</v>
@@ -6477,19 +6466,19 @@
         <v>3</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="G93" s="1" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="K93" s="1">
         <v>1</v>
       </c>
       <c r="L93" s="1" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="M93" s="1">
         <v>2</v>
@@ -6512,10 +6501,10 @@
         <v>3</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="F94" s="1" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="N94" s="1">
         <v>11</v>
@@ -6535,7 +6524,7 @@
         <v>3</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="N95" s="1">
         <v>11</v>
@@ -6555,16 +6544,16 @@
         <v>3</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="F96" s="1" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="K96" s="1">
         <v>1</v>
       </c>
       <c r="L96" s="1" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="M96" s="1">
         <v>2</v>
@@ -6587,10 +6576,10 @@
         <v>3</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="F97" s="1" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="K97" s="1">
         <v>1</v>
@@ -6613,10 +6602,10 @@
         <v>3</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="R98" s="1">
         <v>1</v>
@@ -6630,10 +6619,10 @@
         <v>3</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="F99" s="1" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="K99" s="1">
         <v>1</v>
@@ -6656,10 +6645,10 @@
         <v>3</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="F100" s="1" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="N100" s="1">
         <v>1</v>
@@ -6676,10 +6665,10 @@
         <v>3</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="F101" s="1" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="K101" s="1">
         <v>8</v>
@@ -6702,10 +6691,10 @@
         <v>3</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="F102" s="1" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="K102" s="1">
         <v>8</v>
@@ -6728,10 +6717,10 @@
         <v>3</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="F103" s="1" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="K103" s="1">
         <v>8</v>
@@ -6754,10 +6743,10 @@
         <v>3</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="F104" s="1" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="N104" s="1">
         <v>14</v>
@@ -6774,10 +6763,10 @@
         <v>3</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="F105" s="1" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="R105" s="1">
         <v>-1</v>
@@ -6799,10 +6788,10 @@
         <v>1</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="F107" s="1" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="K107" s="1">
         <v>-1</v>
@@ -6828,13 +6817,13 @@
         <v>1</v>
       </c>
       <c r="D108" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="F108" s="7" t="s">
+        <v>284</v>
+      </c>
+      <c r="G108" s="1" t="s">
         <v>285</v>
-      </c>
-      <c r="F108" s="7" t="s">
-        <v>287</v>
-      </c>
-      <c r="G108" s="1" t="s">
-        <v>288</v>
       </c>
       <c r="M108" s="1">
         <v>2</v>
@@ -6857,13 +6846,13 @@
         <v>1</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="F109" s="7" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="G109" s="1" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="M109" s="1">
         <v>2</v>
@@ -6886,13 +6875,13 @@
         <v>1</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="F110" s="7" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="G110" s="1" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="M110" s="1">
         <v>2</v>
@@ -6915,13 +6904,13 @@
         <v>1</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="F111" s="7" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="G111" s="1" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="M111" s="1">
         <v>2</v>
@@ -6944,10 +6933,10 @@
         <v>1</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="F112" s="1" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="N112" s="1">
         <v>5</v>
@@ -6967,10 +6956,10 @@
         <v>1</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="F113" s="1" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="N113" s="1">
         <v>5</v>
@@ -6990,10 +6979,10 @@
         <v>1</v>
       </c>
       <c r="D114" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="F114" s="1" t="s">
         <v>293</v>
-      </c>
-      <c r="F114" s="1" t="s">
-        <v>296</v>
       </c>
       <c r="N114" s="1">
         <v>5</v>
@@ -7013,10 +7002,10 @@
         <v>1</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="F115" s="1" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="N115" s="1">
         <v>5</v>
@@ -7036,10 +7025,10 @@
         <v>1</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="F116" s="1" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="N116" s="1">
         <v>5</v>
@@ -7059,10 +7048,10 @@
         <v>1</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="F117" s="1" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="N117" s="1">
         <v>5</v>
@@ -7082,10 +7071,10 @@
         <v>1</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="F118" s="1" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="N118" s="1">
         <v>5</v>
@@ -7105,10 +7094,10 @@
         <v>1</v>
       </c>
       <c r="D119" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="F119" s="1" t="s">
         <v>299</v>
-      </c>
-      <c r="F119" s="1" t="s">
-        <v>302</v>
       </c>
       <c r="N119" s="1">
         <v>5</v>
@@ -7128,10 +7117,10 @@
         <v>1</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="F120" s="1" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="N120" s="1">
         <v>5</v>
@@ -7151,10 +7140,10 @@
         <v>1</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="F121" s="1" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="N121" s="1">
         <v>5</v>
@@ -7174,10 +7163,10 @@
         <v>1</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="F122" s="1" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="N122" s="1">
         <v>5</v>
@@ -7197,10 +7186,10 @@
         <v>1</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="F123" s="1" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="N123" s="1">
         <v>5</v>
@@ -7220,10 +7209,10 @@
         <v>1</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="F124" s="1" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="N124" s="1">
         <v>5</v>
@@ -7243,10 +7232,10 @@
         <v>1</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="F125" s="1" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="N125" s="1">
         <v>5</v>
@@ -7266,13 +7255,13 @@
         <v>1</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="F126" s="1" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="L126" s="1" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="N126" s="1">
         <v>5</v>
@@ -7292,13 +7281,13 @@
         <v>1</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="F127" s="1" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="L127" s="1" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="N127" s="1">
         <v>5</v>
@@ -7318,13 +7307,13 @@
         <v>1</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="F128" s="1" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="L128" s="1" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="N128" s="1">
         <v>5</v>
@@ -7344,13 +7333,13 @@
         <v>1</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="F129" s="1" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="L129" s="1" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="N129" s="1">
         <v>5</v>
@@ -7370,16 +7359,16 @@
         <v>1</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="F130" s="1" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="K130" s="1">
         <v>3</v>
       </c>
       <c r="L130" s="1" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="N130" s="1">
         <v>5</v>
@@ -7399,16 +7388,16 @@
         <v>1</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="F131" s="1" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="K131" s="1">
         <v>3</v>
       </c>
       <c r="L131" s="1" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="N131" s="1">
         <v>5</v>
@@ -7428,13 +7417,13 @@
         <v>3</v>
       </c>
       <c r="F132" s="1" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="K132" s="1">
         <v>99</v>
       </c>
       <c r="L132" s="1" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="N132" s="1">
         <v>1</v>
@@ -7454,13 +7443,13 @@
         <v>3</v>
       </c>
       <c r="F133" s="1" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="K133" s="1">
         <v>99</v>
       </c>
       <c r="L133" s="1" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="N133" s="1">
         <v>1</v>
@@ -7480,13 +7469,13 @@
         <v>3</v>
       </c>
       <c r="F134" s="1" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="K134" s="1">
         <v>99</v>
       </c>
       <c r="L134" s="1" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="N134" s="1">
         <v>1</v>
@@ -7506,13 +7495,13 @@
         <v>3</v>
       </c>
       <c r="F135" s="1" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="K135" s="1">
         <v>99</v>
       </c>
       <c r="L135" s="1" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="N135" s="1">
         <v>1</v>
@@ -7532,13 +7521,13 @@
         <v>3</v>
       </c>
       <c r="F136" s="1" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="K136" s="1">
         <v>99</v>
       </c>
       <c r="L136" s="1" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="N136" s="1">
         <v>1</v>
@@ -7558,13 +7547,13 @@
         <v>3</v>
       </c>
       <c r="F137" s="1" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="K137" s="1">
         <v>99</v>
       </c>
       <c r="L137" s="1" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="N137" s="1">
         <v>1</v>
@@ -8003,7 +7992,7 @@
         <v>9</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="C1" s="5" t="s">
         <v>20</v>
@@ -8017,7 +8006,7 @@
         <v>-1</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.15">
@@ -8028,7 +8017,7 @@
         <v>1</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.15">
@@ -8039,7 +8028,7 @@
         <v>1</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.15">
@@ -8050,7 +8039,7 @@
         <v>1</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.15">
@@ -8061,7 +8050,7 @@
         <v>1</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.15">
@@ -8072,7 +8061,7 @@
         <v>2</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.15">
@@ -8083,7 +8072,7 @@
         <v>1</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.15">
@@ -8094,7 +8083,7 @@
         <v>1</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.15">
@@ -8105,7 +8094,7 @@
         <v>1</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.15">
@@ -8116,7 +8105,7 @@
         <v>1</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.15">
@@ -8127,7 +8116,7 @@
         <v>1</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.15">
@@ -8138,7 +8127,7 @@
         <v>1</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.15">
@@ -8157,7 +8146,7 @@
         <v>1</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.15">
@@ -8212,117 +8201,117 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A1" s="2" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A2" s="1" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A3" s="1" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A4" s="1" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A5" s="1" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A6" s="1" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A7" s="1" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A8" s="1" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A9" s="1" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A10" s="1" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A11" s="1" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A12" s="1" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A13" s="1" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A14" s="1" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A15" s="1" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A16" s="1" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A17" s="1" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A18" s="1" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A19" s="1" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A20" s="1" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A21" s="1" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A22" s="1" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A23" s="1" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
     </row>
   </sheetData>

--- a/Luban/Excel/CombatBuff.xlsx
+++ b/Luban/Excel/CombatBuff.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\Return0\Luban\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0440AD3-AB4E-4719-88E9-C1376E3CBC36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5C6D9A1-5C48-4E77-8135-E276136008A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -168,7 +168,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="485" uniqueCount="362">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="491" uniqueCount="367">
   <si>
     <t>类型</t>
   </si>
@@ -242,6 +242,9 @@
     <t>Limit</t>
   </si>
   <si>
+    <t>StackDecrement</t>
+  </si>
+  <si>
     <t>TackingRule</t>
   </si>
   <si>
@@ -300,6 +303,98 @@
     <t>回避</t>
   </si>
   <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>至少减少受到的</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>武杀式</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>{[int]}%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>敌手的力</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>的直接伤害，至少减少行动目标对自身的</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>术杀式</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>伤害{[int]}%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>敌手的技</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>的直接伤害</t>
+    </r>
+  </si>
+  <si>
     <t>1/2/3层提供50/75/100（与盲目状态的效果取最高值）</t>
   </si>
   <si>
@@ -426,6 +521,38 @@
     <t>刚聚</t>
   </si>
   <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>每层使获得的</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFFFFF00"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>刚炁</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>增加{[int]}</t>
+    </r>
+  </si>
+  <si>
     <t>每层使获得的刚炁增加1</t>
   </si>
   <si>
@@ -788,6 +915,9 @@
     <t>行动每加快1息伤害提升5%，每层使行动加快1息</t>
   </si>
   <si>
+    <t>血炁甲</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="10"/>
@@ -823,7 +953,7 @@
     <t>5,6</t>
   </si>
   <si>
-    <t>行字诀</t>
+    <t>稳势</t>
   </si>
   <si>
     <t>行动后获得1个随机的键</t>
@@ -931,7 +1061,7 @@
     <t>伤口</t>
   </si>
   <si>
-    <t>每层使扣除键时同时扣除{[int]}的体</t>
+    <t>每层使键消耗时扣除{[int]}的体</t>
   </si>
   <si>
     <t>6+GR*1.2</t>
@@ -1556,6 +1686,26 @@
     <t>无法使用招式，受到招式的直接攻击或被消除时扣除2层</t>
   </si>
   <si>
+    <t>醉气</t>
+  </si>
+  <si>
+    <r>
+      <t>速</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>-{[int]}</t>
+    </r>
+  </si>
+  <si>
+    <t>80+GR*1</t>
+  </si>
+  <si>
     <t>交鸣</t>
   </si>
   <si>
@@ -1657,12 +1807,6 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
       <t>每20层使</t>
     </r>
     <r>
@@ -2511,6 +2655,9 @@
     <t>被击破时随机转移至另一个友方，若是术杀式击破则扣除1层，完全清除时结束战斗</t>
   </si>
   <si>
+    <t>破招抵免</t>
+  </si>
+  <si>
     <t>药力·刚炁恢复</t>
   </si>
   <si>
@@ -2518,6 +2665,23 @@
   </si>
   <si>
     <r>
+      <t>回合开始</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>固定增加{[int]}刚炁</t>
+    </r>
+  </si>
+  <si>
+    <t>每层7</t>
+  </si>
+  <si>
+    <r>
       <rPr>
         <sz val="10"/>
         <color rgb="FF00B050"/>
@@ -2538,9 +2702,6 @@
     </r>
   </si>
   <si>
-    <t>每层7</t>
-  </si>
-  <si>
     <t>每层25</t>
   </si>
   <si>
@@ -2772,135 +2933,15 @@
     <t>非法咒式</t>
   </si>
   <si>
-    <t>int32</t>
-    <phoneticPr fontId="21" type="noConversion"/>
-  </si>
-  <si>
-    <t>StackDecrement</t>
-    <phoneticPr fontId="21" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>至少减少受到的</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>武杀式</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>{[int]}%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>敌手的力</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>的直接伤害，至少减少行动目标对自身的</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF00B0F0"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>术杀式</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>伤害{[int]}%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF00B0F0"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>敌手的技</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>的直接伤害</t>
-    </r>
-    <phoneticPr fontId="21" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>每层使获得的</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FFFFFF00"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>刚炁</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>增加{[int]}</t>
-    </r>
-    <phoneticPr fontId="21" type="noConversion"/>
-  </si>
-  <si>
-    <t>血炁甲</t>
-    <phoneticPr fontId="21" type="noConversion"/>
+    <t>抵免{[int]}次破招</t>
+    <phoneticPr fontId="22" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="23" x14ac:knownFonts="1">
+  <fonts count="24" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2960,21 +3001,14 @@
     </font>
     <font>
       <sz val="10"/>
-      <color rgb="FFC00000"/>
+      <color rgb="FF92D050"/>
       <name val="微软雅黑"/>
       <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
-      <color rgb="FF7030A0"/>
-      <name val="微软雅黑"/>
-      <family val="2"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF92D050"/>
+      <color theme="9" tint="-0.249977111117893"/>
       <name val="微软雅黑"/>
       <family val="2"/>
       <charset val="134"/>
@@ -2995,13 +3029,6 @@
     </font>
     <font>
       <sz val="10"/>
-      <color theme="9" tint="-0.249977111117893"/>
-      <name val="微软雅黑"/>
-      <family val="2"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
       <color rgb="FFFFFF00"/>
       <name val="微软雅黑"/>
       <family val="2"/>
@@ -3016,7 +3043,21 @@
     </font>
     <font>
       <sz val="10"/>
+      <color rgb="FFC00000"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
       <color theme="9" tint="0.39997558519241921"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF7030A0"/>
       <name val="微软雅黑"/>
       <family val="2"/>
       <charset val="134"/>
@@ -3046,6 +3087,13 @@
       <charset val="134"/>
     </font>
     <font>
+      <b/>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <sz val="9"/>
       <name val="宋体"/>
       <family val="3"/>
@@ -3053,10 +3101,10 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <family val="3"/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
       <charset val="134"/>
     </font>
   </fonts>
@@ -3097,7 +3145,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -3129,6 +3177,12 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -3433,18 +3487,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R174"/>
+  <dimension ref="A1:R176"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="3" width="9" style="1"/>
     <col min="4" max="4" width="16.125" style="1" customWidth="1"/>
     <col min="5" max="5" width="11.5" style="1" customWidth="1"/>
-    <col min="6" max="6" width="137.125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="76.75" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="7.625" style="1" customWidth="1"/>
-    <col min="9" max="10" width="14.125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="61.125" style="1" customWidth="1"/>
+    <col min="7" max="8" width="7.625" style="1" customWidth="1"/>
+    <col min="9" max="9" width="45.25" style="1" customWidth="1"/>
+    <col min="10" max="10" width="14.125" style="1" customWidth="1"/>
     <col min="11" max="11" width="9" style="1"/>
-    <col min="12" max="12" width="15.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9.625" style="1" customWidth="1"/>
     <col min="13" max="13" width="8.375" style="1" customWidth="1"/>
     <col min="14" max="14" width="10.375" style="1" customWidth="1"/>
     <col min="15" max="15" width="15.125" style="1" customWidth="1"/>
@@ -3533,71 +3587,71 @@
         <v>23</v>
       </c>
       <c r="L2" s="6" t="s">
-        <v>358</v>
+        <v>24</v>
       </c>
       <c r="M2" s="6" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="N2" s="6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="O2" s="6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="P2" s="6" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="Q2" s="6" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="R2" s="6"/>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A3" s="6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D3" s="6"/>
       <c r="E3" s="6" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F3" s="6"/>
       <c r="G3" s="6"/>
       <c r="H3" s="6"/>
       <c r="I3" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="J3" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="K3" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="J3" s="6" t="s">
+      <c r="L3" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="M3" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="K3" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="L3" s="6" t="s">
+      <c r="N3" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="M3" s="6" t="s">
-        <v>357</v>
-      </c>
-      <c r="N3" s="6" t="s">
-        <v>29</v>
-      </c>
       <c r="O3" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="P3" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q3" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="P3" s="6" t="s">
+      <c r="R3" s="6" t="s">
         <v>30</v>
-      </c>
-      <c r="Q3" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="R3" s="6" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.15">
@@ -3608,22 +3662,22 @@
         <v>1</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K4" s="1">
         <v>99</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="M4" s="1">
         <v>1</v>
@@ -3646,22 +3700,22 @@
         <v>1</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>359</v>
+        <v>38</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="K5" s="1">
         <v>3</v>
       </c>
       <c r="L5" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="M5" s="1">
         <v>1</v>
@@ -3684,22 +3738,22 @@
         <v>1</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="K6" s="1">
         <v>-1</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="M6" s="1">
         <v>1</v>
@@ -3722,16 +3776,16 @@
         <v>1</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="K7" s="1">
         <v>99</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="M7" s="1">
         <v>1</v>
@@ -3754,22 +3808,22 @@
         <v>1</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="K8" s="1">
         <v>10</v>
       </c>
       <c r="L8" s="1" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="M8" s="1">
         <v>1</v>
@@ -3792,22 +3846,22 @@
         <v>1</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>360</v>
+        <v>55</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="K9" s="1">
         <v>5</v>
       </c>
       <c r="L9" s="1" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="M9" s="1">
         <v>1</v>
@@ -3830,22 +3884,22 @@
         <v>1</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="K10" s="1">
         <v>5</v>
       </c>
       <c r="L10" s="1" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="M10" s="1">
         <v>1</v>
@@ -3868,22 +3922,22 @@
         <v>1</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="K11" s="1">
         <v>5</v>
       </c>
       <c r="L11" s="1" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="M11" s="1">
         <v>1</v>
@@ -3906,22 +3960,22 @@
         <v>1</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="F12" s="8" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="K12" s="1">
         <v>5</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="M12" s="1">
         <v>1</v>
@@ -3944,22 +3998,22 @@
         <v>1</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="K13" s="1">
         <v>5</v>
       </c>
       <c r="L13" s="1" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="M13" s="1">
         <v>1</v>
@@ -3982,19 +4036,19 @@
         <v>1</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="K14" s="1">
         <v>5</v>
       </c>
       <c r="L14" s="1" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="M14" s="1">
         <v>1</v>
@@ -4017,22 +4071,22 @@
         <v>1</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="J15" s="1" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="K15" s="1">
         <v>5</v>
       </c>
       <c r="L15" s="1" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="M15" s="1">
         <v>1</v>
@@ -4052,16 +4106,16 @@
         <v>1</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="K16" s="1">
         <v>1</v>
       </c>
       <c r="L16" s="1" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="M16" s="1">
         <v>2</v>
@@ -4084,16 +4138,16 @@
         <v>1</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="K17" s="1">
         <v>1</v>
       </c>
       <c r="L17" s="1" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="M17" s="1">
         <v>2</v>
@@ -4116,19 +4170,19 @@
         <v>1</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="F18" s="9" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="K18" s="1">
         <v>5</v>
       </c>
       <c r="L18" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="M18" s="1">
         <v>2</v>
@@ -4151,19 +4205,19 @@
         <v>1</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>361</v>
+        <v>90</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="K19" s="1">
         <v>-1</v>
       </c>
       <c r="L19" s="1" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="M19" s="1">
         <v>1</v>
@@ -4186,16 +4240,16 @@
         <v>1</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="K20" s="1">
         <v>-1</v>
       </c>
       <c r="L20" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="M20" s="1">
         <v>2</v>
@@ -4218,16 +4272,16 @@
         <v>1</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="K21" s="1">
         <v>1</v>
       </c>
       <c r="L21" s="1" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="M21" s="1">
         <v>2</v>
@@ -4250,16 +4304,16 @@
         <v>1</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="K22" s="1">
         <v>-1</v>
       </c>
       <c r="L22" s="1" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="M22" s="1">
         <v>2</v>
@@ -4282,16 +4336,16 @@
         <v>1</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="K23" s="1">
         <v>10</v>
       </c>
       <c r="L23" s="1" t="s">
-        <v>35</v>
+        <v>100</v>
       </c>
       <c r="M23" s="1">
         <v>2</v>
@@ -4314,16 +4368,16 @@
         <v>1</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="K24" s="1">
         <v>1</v>
       </c>
       <c r="L24" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="M24" s="1">
         <v>1</v>
@@ -4346,16 +4400,16 @@
         <v>1</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="K25" s="1">
         <v>1</v>
       </c>
       <c r="L25" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="M25" s="1">
         <v>1</v>
@@ -4378,19 +4432,19 @@
         <v>1</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="K26" s="1">
         <v>3</v>
       </c>
       <c r="L26" s="1" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="M26" s="1">
         <v>2</v>
@@ -4407,16 +4461,16 @@
         <v>1</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="K27" s="1">
         <v>99</v>
       </c>
       <c r="L27" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="M27" s="1">
         <v>2</v>
@@ -4433,19 +4487,19 @@
         <v>2</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="K29" s="1">
         <v>10</v>
       </c>
       <c r="L29" s="1" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="M29" s="1">
         <v>1</v>
@@ -4468,19 +4522,19 @@
         <v>2</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="K30" s="1">
         <v>8</v>
       </c>
       <c r="L30" s="1" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="M30" s="1">
         <v>2</v>
@@ -4503,16 +4557,16 @@
         <v>2</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="K31" s="1">
         <v>-1</v>
       </c>
       <c r="L31" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="M31" s="1">
         <v>2</v>
@@ -4535,16 +4589,16 @@
         <v>2</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="K32" s="1">
         <v>-1</v>
       </c>
       <c r="L32" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="M32" s="1">
         <v>2</v>
@@ -4567,16 +4621,16 @@
         <v>2</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="K33" s="1">
         <v>-1</v>
       </c>
       <c r="L33" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="M33" s="1">
         <v>2</v>
@@ -4599,16 +4653,16 @@
         <v>2</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="K34" s="1">
         <v>-1</v>
       </c>
       <c r="L34" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="M34" s="1">
         <v>2</v>
@@ -4631,16 +4685,16 @@
         <v>2</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="K35" s="1">
         <v>-1</v>
       </c>
       <c r="L35" s="1" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="M35" s="1">
         <v>2</v>
@@ -4663,19 +4717,19 @@
         <v>2</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="K36" s="1">
         <v>-1</v>
       </c>
       <c r="L36" s="1" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="M36" s="1">
         <v>1</v>
@@ -4698,19 +4752,19 @@
         <v>2</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="K37" s="1">
         <v>5</v>
       </c>
       <c r="L37" s="1" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="M37" s="1">
         <v>1</v>
@@ -4733,19 +4787,19 @@
         <v>2</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="K38" s="1">
         <v>5</v>
       </c>
       <c r="L38" s="1" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="M38" s="1">
         <v>1</v>
@@ -4768,19 +4822,19 @@
         <v>2</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="F39" s="8" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="K39" s="1">
         <v>5</v>
       </c>
       <c r="L39" s="1" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="M39" s="1">
         <v>1</v>
@@ -4803,19 +4857,19 @@
         <v>2</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="F40" s="8" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="G40" s="1" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="K40" s="1">
         <v>5</v>
       </c>
       <c r="L40" s="1" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="M40" s="1">
         <v>1</v>
@@ -4838,22 +4892,22 @@
         <v>2</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="F41" s="8" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="J41" s="1" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="K41" s="1">
         <v>5</v>
       </c>
       <c r="L41" s="1" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="M41" s="1">
         <v>1</v>
@@ -4876,22 +4930,22 @@
         <v>2</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="F42" s="8" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="G42" s="1" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="J42" s="1" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="K42" s="1">
         <v>5</v>
       </c>
       <c r="L42" s="1" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="M42" s="1">
         <v>1</v>
@@ -4914,16 +4968,16 @@
         <v>2</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="K43" s="1">
         <v>1</v>
       </c>
       <c r="L43" s="1" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="M43" s="1">
         <v>1</v>
@@ -4946,16 +5000,16 @@
         <v>2</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="K44" s="1">
         <v>2</v>
       </c>
       <c r="L44" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="M44" s="1">
         <v>1</v>
@@ -4978,19 +5032,19 @@
         <v>2</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="G45" s="1" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="K45" s="1">
         <v>3</v>
       </c>
       <c r="L45" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="M45" s="1">
         <v>1</v>
@@ -5013,16 +5067,16 @@
         <v>2</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="K46" s="1">
         <v>5</v>
       </c>
       <c r="L46" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="M46" s="1">
         <v>2</v>
@@ -5045,16 +5099,16 @@
         <v>2</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="K47" s="1">
         <v>5</v>
       </c>
       <c r="L47" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="M47" s="1">
         <v>2</v>
@@ -5077,16 +5131,16 @@
         <v>2</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="K48" s="1">
         <v>5</v>
       </c>
       <c r="L48" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="M48" s="1">
         <v>2</v>
@@ -5109,16 +5163,16 @@
         <v>2</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="K49" s="1">
         <v>5</v>
       </c>
       <c r="L49" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="M49" s="1">
         <v>2</v>
@@ -5141,10 +5195,10 @@
         <v>2</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="F50" s="7" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="K50" s="1">
         <v>10</v>
@@ -5170,10 +5224,10 @@
         <v>2</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="F51" s="7" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="K51" s="1">
         <v>-1</v>
@@ -5199,16 +5253,16 @@
         <v>2</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="F52" s="7" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="K52" s="1">
         <v>1</v>
       </c>
       <c r="L52" s="1" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="M52" s="1">
         <v>2</v>
@@ -5231,16 +5285,16 @@
         <v>2</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="F53" s="7" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="K53" s="1">
         <v>1</v>
       </c>
       <c r="L53" s="1" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="M53" s="1">
         <v>2</v>
@@ -5263,16 +5317,16 @@
         <v>2</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="F54" s="7" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="K54" s="1">
         <v>1</v>
       </c>
       <c r="L54" s="1" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="M54" s="1">
         <v>2</v>
@@ -5295,16 +5349,16 @@
         <v>2</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="F55" s="7" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="K55" s="1">
         <v>1</v>
       </c>
       <c r="L55" s="1" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="M55" s="1">
         <v>2</v>
@@ -5327,16 +5381,16 @@
         <v>2</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="K56" s="1">
         <v>-1</v>
       </c>
       <c r="L56" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="M56" s="1">
         <v>2</v>
@@ -5359,10 +5413,10 @@
         <v>2</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="G57" s="10">
         <v>1</v>
@@ -5373,7 +5427,7 @@
         <v>-1</v>
       </c>
       <c r="L57" s="1" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="M57" s="1">
         <v>2</v>
@@ -5396,19 +5450,19 @@
         <v>2</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="G58" s="1" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="K58" s="1">
         <v>5</v>
       </c>
       <c r="L58" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="M58" s="1">
         <v>1</v>
@@ -5431,19 +5485,19 @@
         <v>2</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="G59" s="1" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="K59" s="1">
         <v>5</v>
       </c>
       <c r="L59" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="M59" s="1">
         <v>1</v>
@@ -5466,16 +5520,16 @@
         <v>2</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="F60" s="8" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="K60" s="1">
         <v>1</v>
       </c>
       <c r="L60" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="M60" s="1">
         <v>1</v>
@@ -5498,16 +5552,16 @@
         <v>2</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="F61" s="8" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="K61" s="1">
         <v>1</v>
       </c>
       <c r="L61" s="1" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="M61" s="1">
         <v>2</v>
@@ -5530,16 +5584,16 @@
         <v>2</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="F62" s="7" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="K62" s="1">
         <v>10</v>
       </c>
       <c r="L62" s="1" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="M62" s="1">
         <v>1</v>
@@ -5562,16 +5616,16 @@
         <v>2</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="F63" s="8" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="K63" s="1">
         <v>-1</v>
       </c>
       <c r="L63" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="M63" s="1">
         <v>1</v>
@@ -5581,64 +5635,49 @@
       </c>
     </row>
     <row r="64" spans="1:18" x14ac:dyDescent="0.15">
-      <c r="F64" s="7"/>
-      <c r="R64" s="1">
-        <v>1</v>
+      <c r="A64" s="1">
+        <v>72036</v>
+      </c>
+      <c r="B64" s="1">
+        <v>2</v>
+      </c>
+      <c r="D64" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="F64" s="11" t="s">
+        <v>199</v>
+      </c>
+      <c r="G64" s="1" t="s">
+        <v>200</v>
       </c>
     </row>
     <row r="65" spans="1:18" x14ac:dyDescent="0.15">
-      <c r="A65" s="1">
-        <v>73001</v>
-      </c>
-      <c r="B65" s="1">
-        <v>3</v>
-      </c>
-      <c r="D65" s="1" t="s">
-        <v>194</v>
-      </c>
-      <c r="F65" s="7" t="s">
-        <v>195</v>
-      </c>
-      <c r="G65" s="1">
-        <v>30</v>
-      </c>
-      <c r="L65" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="M65" s="1">
-        <v>1</v>
-      </c>
-      <c r="N65" s="1">
-        <v>1</v>
-      </c>
-      <c r="Q65" s="1">
-        <v>1</v>
-      </c>
+      <c r="F65" s="7"/>
       <c r="R65" s="1">
         <v>1</v>
       </c>
     </row>
     <row r="66" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A66" s="1">
-        <v>73002</v>
+        <v>73001</v>
       </c>
       <c r="B66" s="1">
         <v>3</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>196</v>
-      </c>
-      <c r="F66" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="K66" s="1">
-        <v>1</v>
+        <v>201</v>
+      </c>
+      <c r="F66" s="7" t="s">
+        <v>202</v>
+      </c>
+      <c r="G66" s="1">
+        <v>30</v>
       </c>
       <c r="L66" s="1" t="s">
-        <v>35</v>
+        <v>195</v>
       </c>
       <c r="M66" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N66" s="1">
         <v>1</v>
@@ -5652,22 +5691,22 @@
     </row>
     <row r="67" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A67" s="1">
-        <v>73003</v>
+        <v>73002</v>
       </c>
       <c r="B67" s="1">
         <v>3</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="K67" s="1">
         <v>1</v>
       </c>
       <c r="L67" s="1" t="s">
-        <v>81</v>
+        <v>36</v>
       </c>
       <c r="M67" s="1">
         <v>2</v>
@@ -5684,25 +5723,22 @@
     </row>
     <row r="68" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A68" s="1">
-        <v>73004</v>
+        <v>73003</v>
       </c>
       <c r="B68" s="1">
         <v>3</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>200</v>
-      </c>
-      <c r="F68" s="7" t="s">
-        <v>201</v>
-      </c>
-      <c r="G68" s="1" t="s">
-        <v>202</v>
+        <v>205</v>
+      </c>
+      <c r="F68" s="1" t="s">
+        <v>206</v>
       </c>
       <c r="K68" s="1">
         <v>1</v>
       </c>
       <c r="L68" s="1" t="s">
-        <v>203</v>
+        <v>84</v>
       </c>
       <c r="M68" s="1">
         <v>2</v>
@@ -5719,25 +5755,28 @@
     </row>
     <row r="69" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A69" s="1">
-        <v>73005</v>
+        <v>73004</v>
       </c>
       <c r="B69" s="1">
         <v>3</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>204</v>
-      </c>
-      <c r="F69" s="8" t="s">
-        <v>205</v>
+        <v>207</v>
+      </c>
+      <c r="F69" s="7" t="s">
+        <v>208</v>
       </c>
       <c r="G69" s="1" t="s">
-        <v>206</v>
+        <v>209</v>
+      </c>
+      <c r="K69" s="1">
+        <v>1</v>
       </c>
       <c r="L69" s="1" t="s">
-        <v>88</v>
+        <v>210</v>
       </c>
       <c r="M69" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N69" s="1">
         <v>1</v>
@@ -5751,25 +5790,25 @@
     </row>
     <row r="70" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A70" s="1">
-        <v>73006</v>
+        <v>73005</v>
       </c>
       <c r="B70" s="1">
         <v>3</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>207</v>
-      </c>
-      <c r="F70" s="1" t="s">
-        <v>208</v>
-      </c>
-      <c r="K70" s="1">
-        <v>1</v>
+        <v>211</v>
+      </c>
+      <c r="F70" s="8" t="s">
+        <v>212</v>
+      </c>
+      <c r="G70" s="1" t="s">
+        <v>213</v>
       </c>
       <c r="L70" s="1" t="s">
-        <v>209</v>
+        <v>92</v>
       </c>
       <c r="M70" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N70" s="1">
         <v>1</v>
@@ -5778,65 +5817,65 @@
         <v>1</v>
       </c>
       <c r="R70" s="1">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="71" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A71" s="1">
-        <v>73007</v>
+        <v>73006</v>
       </c>
       <c r="B71" s="1">
         <v>3</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>210</v>
-      </c>
-      <c r="F71" s="7" t="s">
-        <v>211</v>
+        <v>214</v>
+      </c>
+      <c r="F71" s="1" t="s">
+        <v>215</v>
       </c>
       <c r="K71" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L71" s="1" t="s">
-        <v>51</v>
+        <v>216</v>
       </c>
       <c r="M71" s="1">
         <v>2</v>
       </c>
       <c r="N71" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Q71" s="1">
         <v>1</v>
       </c>
       <c r="R71" s="1">
-        <v>1</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="72" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A72" s="1">
-        <v>73008</v>
+        <v>73007</v>
       </c>
       <c r="B72" s="1">
         <v>3</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="F72" s="7" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="K72" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L72" s="1" t="s">
-        <v>81</v>
+        <v>53</v>
       </c>
       <c r="M72" s="1">
         <v>2</v>
       </c>
       <c r="N72" s="1">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="Q72" s="1">
         <v>1</v>
@@ -5847,22 +5886,28 @@
     </row>
     <row r="73" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A73" s="1">
-        <v>73009</v>
+        <v>73008</v>
       </c>
       <c r="B73" s="1">
         <v>3</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="F73" s="7" t="s">
-        <v>215</v>
-      </c>
-      <c r="G73" s="1" t="s">
-        <v>216</v>
+        <v>220</v>
+      </c>
+      <c r="K73" s="1">
+        <v>1</v>
+      </c>
+      <c r="L73" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="M73" s="1">
+        <v>2</v>
       </c>
       <c r="N73" s="1">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="Q73" s="1">
         <v>1</v>
@@ -5873,19 +5918,22 @@
     </row>
     <row r="74" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A74" s="1">
-        <v>73010</v>
+        <v>73009</v>
       </c>
       <c r="B74" s="1">
         <v>3</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>217</v>
-      </c>
-      <c r="F74" s="9" t="s">
-        <v>218</v>
+        <v>221</v>
+      </c>
+      <c r="F74" s="7" t="s">
+        <v>222</v>
+      </c>
+      <c r="G74" s="1" t="s">
+        <v>223</v>
       </c>
       <c r="N74" s="1">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="Q74" s="1">
         <v>1</v>
@@ -5896,28 +5944,19 @@
     </row>
     <row r="75" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A75" s="1">
-        <v>73011</v>
+        <v>73010</v>
       </c>
       <c r="B75" s="1">
         <v>3</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>219</v>
-      </c>
-      <c r="F75" s="7" t="s">
-        <v>220</v>
-      </c>
-      <c r="K75" s="1">
-        <v>1</v>
-      </c>
-      <c r="L75" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="M75" s="1">
-        <v>2</v>
+        <v>224</v>
+      </c>
+      <c r="F75" s="9" t="s">
+        <v>225</v>
       </c>
       <c r="N75" s="1">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Q75" s="1">
         <v>1</v>
@@ -5928,22 +5967,22 @@
     </row>
     <row r="76" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A76" s="1">
-        <v>73012</v>
+        <v>73011</v>
       </c>
       <c r="B76" s="1">
         <v>3</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="F76" s="7" t="s">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="K76" s="1">
         <v>1</v>
       </c>
       <c r="L76" s="1" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="M76" s="1">
         <v>2</v>
@@ -5960,22 +5999,22 @@
     </row>
     <row r="77" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A77" s="1">
-        <v>73013</v>
+        <v>73012</v>
       </c>
       <c r="B77" s="1">
         <v>3</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="F77" s="7" t="s">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="K77" s="1">
         <v>1</v>
       </c>
       <c r="L77" s="1" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="M77" s="1">
         <v>2</v>
@@ -5992,22 +6031,22 @@
     </row>
     <row r="78" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A78" s="1">
-        <v>73014</v>
+        <v>73013</v>
       </c>
       <c r="B78" s="1">
         <v>3</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="F78" s="7" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="K78" s="1">
         <v>1</v>
       </c>
       <c r="L78" s="1" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="M78" s="1">
         <v>2</v>
@@ -6024,22 +6063,22 @@
     </row>
     <row r="79" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A79" s="1">
-        <v>73015</v>
+        <v>73014</v>
       </c>
       <c r="B79" s="1">
         <v>3</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c r="F79" s="7" t="s">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="K79" s="1">
         <v>1</v>
       </c>
       <c r="L79" s="1" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="M79" s="1">
         <v>2</v>
@@ -6056,22 +6095,22 @@
     </row>
     <row r="80" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A80" s="1">
-        <v>73016</v>
+        <v>73015</v>
       </c>
       <c r="B80" s="1">
         <v>3</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="F80" s="7" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="K80" s="1">
         <v>1</v>
       </c>
       <c r="L80" s="1" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="M80" s="1">
         <v>2</v>
@@ -6088,22 +6127,22 @@
     </row>
     <row r="81" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A81" s="1">
-        <v>73017</v>
+        <v>73016</v>
       </c>
       <c r="B81" s="1">
         <v>3</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="F81" s="7" t="s">
-        <v>232</v>
+        <v>237</v>
       </c>
       <c r="K81" s="1">
         <v>1</v>
       </c>
       <c r="L81" s="1" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="M81" s="1">
         <v>2</v>
@@ -6120,22 +6159,22 @@
     </row>
     <row r="82" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A82" s="1">
-        <v>73018</v>
+        <v>73017</v>
       </c>
       <c r="B82" s="1">
         <v>3</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="F82" s="7" t="s">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="K82" s="1">
         <v>1</v>
       </c>
       <c r="L82" s="1" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="M82" s="1">
         <v>2</v>
@@ -6152,22 +6191,22 @@
     </row>
     <row r="83" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A83" s="1">
-        <v>73019</v>
+        <v>73018</v>
       </c>
       <c r="B83" s="1">
         <v>3</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="F83" s="7" t="s">
-        <v>236</v>
+        <v>241</v>
       </c>
       <c r="K83" s="1">
         <v>1</v>
       </c>
       <c r="L83" s="1" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="M83" s="1">
         <v>2</v>
@@ -6184,22 +6223,22 @@
     </row>
     <row r="84" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A84" s="1">
-        <v>73020</v>
+        <v>73019</v>
       </c>
       <c r="B84" s="1">
         <v>3</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>237</v>
+        <v>242</v>
       </c>
       <c r="F84" s="7" t="s">
-        <v>238</v>
+        <v>243</v>
       </c>
       <c r="K84" s="1">
         <v>1</v>
       </c>
       <c r="L84" s="1" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="M84" s="1">
         <v>2</v>
@@ -6216,22 +6255,22 @@
     </row>
     <row r="85" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A85" s="1">
-        <v>73021</v>
+        <v>73020</v>
       </c>
       <c r="B85" s="1">
         <v>3</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="F85" s="7" t="s">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="K85" s="1">
         <v>1</v>
       </c>
       <c r="L85" s="1" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="M85" s="1">
         <v>2</v>
@@ -6248,22 +6287,22 @@
     </row>
     <row r="86" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A86" s="1">
-        <v>73022</v>
+        <v>73021</v>
       </c>
       <c r="B86" s="1">
         <v>3</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="F86" s="7" t="s">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="K86" s="1">
         <v>1</v>
       </c>
       <c r="L86" s="1" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="M86" s="1">
         <v>2</v>
@@ -6280,22 +6319,22 @@
     </row>
     <row r="87" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A87" s="1">
-        <v>73023</v>
+        <v>73022</v>
       </c>
       <c r="B87" s="1">
         <v>3</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="F87" s="7" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="K87" s="1">
         <v>1</v>
       </c>
       <c r="L87" s="1" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="M87" s="1">
         <v>2</v>
@@ -6312,22 +6351,22 @@
     </row>
     <row r="88" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A88" s="1">
-        <v>73024</v>
+        <v>73023</v>
       </c>
       <c r="B88" s="1">
         <v>3</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="F88" s="7" t="s">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="K88" s="1">
         <v>1</v>
       </c>
       <c r="L88" s="1" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="M88" s="1">
         <v>2</v>
@@ -6344,22 +6383,22 @@
     </row>
     <row r="89" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A89" s="1">
-        <v>73025</v>
+        <v>73024</v>
       </c>
       <c r="B89" s="1">
         <v>3</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="F89" s="7" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="K89" s="1">
         <v>1</v>
       </c>
       <c r="L89" s="1" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="M89" s="1">
         <v>2</v>
@@ -6376,22 +6415,22 @@
     </row>
     <row r="90" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A90" s="1">
-        <v>73026</v>
+        <v>73025</v>
       </c>
       <c r="B90" s="1">
         <v>3</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="F90" s="7" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="K90" s="1">
         <v>1</v>
       </c>
       <c r="L90" s="1" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="M90" s="1">
         <v>2</v>
@@ -6408,25 +6447,28 @@
     </row>
     <row r="91" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A91" s="1">
-        <v>73027</v>
+        <v>73026</v>
       </c>
       <c r="B91" s="1">
         <v>3</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>251</v>
-      </c>
-      <c r="F91" s="9" t="s">
-        <v>252</v>
-      </c>
-      <c r="G91" s="1" t="s">
-        <v>253</v>
+        <v>256</v>
+      </c>
+      <c r="F91" s="7" t="s">
+        <v>257</v>
       </c>
       <c r="K91" s="1">
         <v>1</v>
       </c>
+      <c r="L91" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="M91" s="1">
+        <v>2</v>
+      </c>
       <c r="N91" s="1">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="Q91" s="1">
         <v>1</v>
@@ -6437,16 +6479,22 @@
     </row>
     <row r="92" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A92" s="1">
-        <v>73028</v>
+        <v>73027</v>
       </c>
       <c r="B92" s="1">
         <v>3</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>254</v>
-      </c>
-      <c r="F92" s="1" t="s">
-        <v>255</v>
+        <v>258</v>
+      </c>
+      <c r="F92" s="9" t="s">
+        <v>259</v>
+      </c>
+      <c r="G92" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="K92" s="1">
+        <v>1</v>
       </c>
       <c r="N92" s="1">
         <v>1</v>
@@ -6460,31 +6508,19 @@
     </row>
     <row r="93" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A93" s="1">
-        <v>73029</v>
+        <v>73028</v>
       </c>
       <c r="B93" s="1">
         <v>3</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="G93" s="1" t="s">
-        <v>258</v>
-      </c>
-      <c r="K93" s="1">
-        <v>1</v>
-      </c>
-      <c r="L93" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="M93" s="1">
-        <v>2</v>
+        <v>262</v>
       </c>
       <c r="N93" s="1">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="Q93" s="1">
         <v>1</v>
@@ -6495,16 +6531,28 @@
     </row>
     <row r="94" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A94" s="1">
-        <v>73030</v>
+        <v>73029</v>
       </c>
       <c r="B94" s="1">
         <v>3</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="F94" s="1" t="s">
-        <v>260</v>
+        <v>264</v>
+      </c>
+      <c r="G94" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="K94" s="1">
+        <v>1</v>
+      </c>
+      <c r="L94" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="M94" s="1">
+        <v>2</v>
       </c>
       <c r="N94" s="1">
         <v>11</v>
@@ -6518,13 +6566,16 @@
     </row>
     <row r="95" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A95" s="1">
-        <v>73031</v>
+        <v>73030</v>
       </c>
       <c r="B95" s="1">
         <v>3</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>261</v>
+        <v>266</v>
+      </c>
+      <c r="F95" s="1" t="s">
+        <v>267</v>
       </c>
       <c r="N95" s="1">
         <v>11</v>
@@ -6538,28 +6589,16 @@
     </row>
     <row r="96" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A96" s="1">
-        <v>73032</v>
+        <v>73031</v>
       </c>
       <c r="B96" s="1">
         <v>3</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>262</v>
-      </c>
-      <c r="F96" s="1" t="s">
-        <v>263</v>
-      </c>
-      <c r="K96" s="1">
-        <v>1</v>
-      </c>
-      <c r="L96" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="M96" s="1">
-        <v>2</v>
+        <v>268</v>
       </c>
       <c r="N96" s="1">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="Q96" s="1">
         <v>1</v>
@@ -6570,25 +6609,31 @@
     </row>
     <row r="97" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A97" s="1">
-        <v>73033</v>
+        <v>73032</v>
       </c>
       <c r="B97" s="1">
         <v>3</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="F97" s="1" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="K97" s="1">
         <v>1</v>
       </c>
       <c r="L97" s="1" t="s">
-        <v>35</v>
+        <v>58</v>
       </c>
       <c r="M97" s="1">
         <v>2</v>
+      </c>
+      <c r="N97" s="1">
+        <v>1</v>
+      </c>
+      <c r="Q97" s="1">
+        <v>1</v>
       </c>
       <c r="R97" s="1">
         <v>1</v>
@@ -6596,16 +6641,28 @@
     </row>
     <row r="98" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A98" s="1">
-        <v>73034</v>
+        <v>73033</v>
       </c>
       <c r="B98" s="1">
         <v>3</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>267</v>
+        <v>272</v>
+      </c>
+      <c r="K98" s="1">
+        <v>1</v>
+      </c>
+      <c r="L98" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="M98" s="1">
+        <v>2</v>
+      </c>
+      <c r="Q98" s="1">
+        <v>1</v>
       </c>
       <c r="R98" s="1">
         <v>1</v>
@@ -6613,25 +6670,19 @@
     </row>
     <row r="99" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A99" s="1">
-        <v>73035</v>
+        <v>73034</v>
       </c>
       <c r="B99" s="1">
         <v>3</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="F99" s="1" t="s">
-        <v>269</v>
-      </c>
-      <c r="K99" s="1">
-        <v>1</v>
-      </c>
-      <c r="L99" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="M99" s="1">
-        <v>2</v>
+        <v>274</v>
+      </c>
+      <c r="Q99" s="1">
+        <v>1</v>
       </c>
       <c r="R99" s="1">
         <v>1</v>
@@ -6639,18 +6690,27 @@
     </row>
     <row r="100" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A100" s="1">
-        <v>73036</v>
+        <v>73035</v>
       </c>
       <c r="B100" s="1">
         <v>3</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="F100" s="1" t="s">
-        <v>271</v>
-      </c>
-      <c r="N100" s="1">
+        <v>276</v>
+      </c>
+      <c r="K100" s="1">
+        <v>1</v>
+      </c>
+      <c r="L100" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="M100" s="1">
+        <v>2</v>
+      </c>
+      <c r="Q100" s="1">
         <v>1</v>
       </c>
       <c r="R100" s="1">
@@ -6659,25 +6719,22 @@
     </row>
     <row r="101" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A101" s="1">
-        <v>73037</v>
+        <v>73036</v>
       </c>
       <c r="B101" s="1">
         <v>3</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="F101" s="1" t="s">
-        <v>273</v>
-      </c>
-      <c r="K101" s="1">
-        <v>8</v>
-      </c>
-      <c r="L101" s="1" t="s">
-        <v>35</v>
+        <v>278</v>
       </c>
       <c r="N101" s="1">
-        <v>14</v>
+        <v>1</v>
+      </c>
+      <c r="Q101" s="1">
+        <v>1</v>
       </c>
       <c r="R101" s="1">
         <v>1</v>
@@ -6685,122 +6742,158 @@
     </row>
     <row r="102" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A102" s="1">
-        <v>73038</v>
+        <v>73037</v>
       </c>
       <c r="B102" s="1">
         <v>3</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="F102" s="1" t="s">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="K102" s="1">
         <v>8</v>
       </c>
       <c r="L102" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="N102" s="1">
         <v>14</v>
       </c>
+      <c r="Q102" s="1">
+        <v>1</v>
+      </c>
       <c r="R102" s="1">
         <v>1</v>
       </c>
     </row>
     <row r="103" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A103" s="1">
-        <v>73039</v>
+        <v>73038</v>
       </c>
       <c r="B103" s="1">
         <v>3</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="F103" s="1" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="K103" s="1">
         <v>8</v>
       </c>
       <c r="L103" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="N103" s="1">
         <v>14</v>
       </c>
+      <c r="Q103" s="1">
+        <v>1</v>
+      </c>
       <c r="R103" s="1">
         <v>1</v>
       </c>
     </row>
     <row r="104" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A104" s="1">
-        <v>73040</v>
+        <v>73039</v>
       </c>
       <c r="B104" s="1">
         <v>3</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="F104" s="1" t="s">
-        <v>279</v>
+        <v>284</v>
+      </c>
+      <c r="K104" s="1">
+        <v>8</v>
+      </c>
+      <c r="L104" s="1" t="s">
+        <v>36</v>
       </c>
       <c r="N104" s="1">
         <v>14</v>
       </c>
+      <c r="Q104" s="1">
+        <v>1</v>
+      </c>
       <c r="R104" s="1">
         <v>1</v>
       </c>
     </row>
     <row r="105" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A105" s="1">
-        <v>73041</v>
+        <v>73040</v>
       </c>
       <c r="B105" s="1">
         <v>3</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="F105" s="1" t="s">
-        <v>281</v>
+        <v>286</v>
+      </c>
+      <c r="N105" s="1">
+        <v>14</v>
+      </c>
+      <c r="Q105" s="1">
+        <v>1</v>
       </c>
       <c r="R105" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="106" spans="1:18" x14ac:dyDescent="0.15">
+      <c r="A106" s="1">
+        <v>73041</v>
+      </c>
+      <c r="B106" s="1">
+        <v>3</v>
+      </c>
+      <c r="D106" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="F106" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="Q106" s="1">
+        <v>1</v>
+      </c>
+      <c r="R106" s="1">
         <v>-1</v>
-      </c>
-    </row>
-    <row r="106" spans="1:18" x14ac:dyDescent="0.15">
-      <c r="Q106" s="1">
-        <v>1</v>
-      </c>
-      <c r="R106" s="1">
-        <v>1</v>
       </c>
     </row>
     <row r="107" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A107" s="1">
-        <v>71501</v>
+        <v>73042</v>
       </c>
       <c r="B107" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>282</v>
-      </c>
-      <c r="F107" s="1" t="s">
-        <v>283</v>
+        <v>289</v>
+      </c>
+      <c r="F107" s="12" t="s">
+        <v>366</v>
       </c>
       <c r="K107" s="1">
-        <v>-1</v>
+        <v>99</v>
+      </c>
+      <c r="L107" s="1" t="s">
+        <v>84</v>
       </c>
       <c r="M107" s="1">
         <v>2</v>
       </c>
       <c r="N107" s="1">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="Q107" s="1">
         <v>1</v>
@@ -6810,27 +6903,6 @@
       </c>
     </row>
     <row r="108" spans="1:18" x14ac:dyDescent="0.15">
-      <c r="A108" s="1">
-        <v>71502</v>
-      </c>
-      <c r="B108" s="1">
-        <v>1</v>
-      </c>
-      <c r="D108" s="1" t="s">
-        <v>282</v>
-      </c>
-      <c r="F108" s="7" t="s">
-        <v>284</v>
-      </c>
-      <c r="G108" s="1" t="s">
-        <v>285</v>
-      </c>
-      <c r="M108" s="1">
-        <v>2</v>
-      </c>
-      <c r="N108" s="1">
-        <v>5</v>
-      </c>
       <c r="Q108" s="1">
         <v>1</v>
       </c>
@@ -6840,19 +6912,19 @@
     </row>
     <row r="109" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A109" s="1">
-        <v>71503</v>
+        <v>71501</v>
       </c>
       <c r="B109" s="1">
         <v>1</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>282</v>
-      </c>
-      <c r="F109" s="7" t="s">
-        <v>284</v>
-      </c>
-      <c r="G109" s="1" t="s">
-        <v>286</v>
+        <v>290</v>
+      </c>
+      <c r="F109" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="K109" s="1">
+        <v>-1</v>
       </c>
       <c r="M109" s="1">
         <v>2</v>
@@ -6869,19 +6941,19 @@
     </row>
     <row r="110" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A110" s="1">
-        <v>71504</v>
+        <v>71502</v>
       </c>
       <c r="B110" s="1">
         <v>1</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>282</v>
+        <v>290</v>
       </c>
       <c r="F110" s="7" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="G110" s="1" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="M110" s="1">
         <v>2</v>
@@ -6898,19 +6970,19 @@
     </row>
     <row r="111" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A111" s="1">
-        <v>71505</v>
+        <v>71503</v>
       </c>
       <c r="B111" s="1">
         <v>1</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>282</v>
+        <v>290</v>
       </c>
       <c r="F111" s="7" t="s">
-        <v>284</v>
+        <v>294</v>
       </c>
       <c r="G111" s="1" t="s">
-        <v>289</v>
+        <v>295</v>
       </c>
       <c r="M111" s="1">
         <v>2</v>
@@ -6927,7 +6999,7 @@
     </row>
     <row r="112" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A112" s="1">
-        <v>71506</v>
+        <v>71504</v>
       </c>
       <c r="B112" s="1">
         <v>1</v>
@@ -6935,8 +7007,14 @@
       <c r="D112" s="1" t="s">
         <v>290</v>
       </c>
-      <c r="F112" s="1" t="s">
-        <v>291</v>
+      <c r="F112" s="7" t="s">
+        <v>296</v>
+      </c>
+      <c r="G112" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="M112" s="1">
+        <v>2</v>
       </c>
       <c r="N112" s="1">
         <v>5</v>
@@ -6950,7 +7028,7 @@
     </row>
     <row r="113" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A113" s="1">
-        <v>71507</v>
+        <v>71505</v>
       </c>
       <c r="B113" s="1">
         <v>1</v>
@@ -6958,8 +7036,14 @@
       <c r="D113" s="1" t="s">
         <v>290</v>
       </c>
-      <c r="F113" s="1" t="s">
-        <v>292</v>
+      <c r="F113" s="7" t="s">
+        <v>294</v>
+      </c>
+      <c r="G113" s="1" t="s">
+        <v>298</v>
+      </c>
+      <c r="M113" s="1">
+        <v>2</v>
       </c>
       <c r="N113" s="1">
         <v>5</v>
@@ -6973,16 +7057,16 @@
     </row>
     <row r="114" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A114" s="1">
-        <v>71508</v>
+        <v>71506</v>
       </c>
       <c r="B114" s="1">
         <v>1</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>290</v>
+        <v>299</v>
       </c>
       <c r="F114" s="1" t="s">
-        <v>293</v>
+        <v>300</v>
       </c>
       <c r="N114" s="1">
         <v>5</v>
@@ -6996,16 +7080,16 @@
     </row>
     <row r="115" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A115" s="1">
-        <v>71509</v>
+        <v>71507</v>
       </c>
       <c r="B115" s="1">
         <v>1</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>290</v>
+        <v>299</v>
       </c>
       <c r="F115" s="1" t="s">
-        <v>294</v>
+        <v>301</v>
       </c>
       <c r="N115" s="1">
         <v>5</v>
@@ -7019,16 +7103,16 @@
     </row>
     <row r="116" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A116" s="1">
-        <v>71510</v>
+        <v>71508</v>
       </c>
       <c r="B116" s="1">
         <v>1</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>290</v>
+        <v>299</v>
       </c>
       <c r="F116" s="1" t="s">
-        <v>295</v>
+        <v>302</v>
       </c>
       <c r="N116" s="1">
         <v>5</v>
@@ -7042,16 +7126,16 @@
     </row>
     <row r="117" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A117" s="1">
-        <v>71511</v>
+        <v>71509</v>
       </c>
       <c r="B117" s="1">
         <v>1</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="F117" s="1" t="s">
-        <v>297</v>
+        <v>303</v>
       </c>
       <c r="N117" s="1">
         <v>5</v>
@@ -7065,16 +7149,16 @@
     </row>
     <row r="118" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A118" s="1">
-        <v>71512</v>
+        <v>71510</v>
       </c>
       <c r="B118" s="1">
         <v>1</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="F118" s="1" t="s">
-        <v>298</v>
+        <v>304</v>
       </c>
       <c r="N118" s="1">
         <v>5</v>
@@ -7088,16 +7172,16 @@
     </row>
     <row r="119" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A119" s="1">
-        <v>71513</v>
+        <v>71511</v>
       </c>
       <c r="B119" s="1">
         <v>1</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>296</v>
+        <v>305</v>
       </c>
       <c r="F119" s="1" t="s">
-        <v>299</v>
+        <v>306</v>
       </c>
       <c r="N119" s="1">
         <v>5</v>
@@ -7111,16 +7195,16 @@
     </row>
     <row r="120" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A120" s="1">
-        <v>71514</v>
+        <v>71512</v>
       </c>
       <c r="B120" s="1">
         <v>1</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>296</v>
+        <v>305</v>
       </c>
       <c r="F120" s="1" t="s">
-        <v>300</v>
+        <v>307</v>
       </c>
       <c r="N120" s="1">
         <v>5</v>
@@ -7134,16 +7218,16 @@
     </row>
     <row r="121" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A121" s="1">
-        <v>71515</v>
+        <v>71513</v>
       </c>
       <c r="B121" s="1">
         <v>1</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>296</v>
+        <v>305</v>
       </c>
       <c r="F121" s="1" t="s">
-        <v>301</v>
+        <v>308</v>
       </c>
       <c r="N121" s="1">
         <v>5</v>
@@ -7157,16 +7241,16 @@
     </row>
     <row r="122" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A122" s="1">
-        <v>71516</v>
+        <v>71514</v>
       </c>
       <c r="B122" s="1">
         <v>1</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>296</v>
+        <v>305</v>
       </c>
       <c r="F122" s="1" t="s">
-        <v>302</v>
+        <v>309</v>
       </c>
       <c r="N122" s="1">
         <v>5</v>
@@ -7180,16 +7264,16 @@
     </row>
     <row r="123" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A123" s="1">
-        <v>71517</v>
+        <v>71515</v>
       </c>
       <c r="B123" s="1">
         <v>1</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>296</v>
+        <v>305</v>
       </c>
       <c r="F123" s="1" t="s">
-        <v>303</v>
+        <v>310</v>
       </c>
       <c r="N123" s="1">
         <v>5</v>
@@ -7203,16 +7287,16 @@
     </row>
     <row r="124" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A124" s="1">
-        <v>71518</v>
+        <v>71516</v>
       </c>
       <c r="B124" s="1">
         <v>1</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="F124" s="1" t="s">
-        <v>305</v>
+        <v>311</v>
       </c>
       <c r="N124" s="1">
         <v>5</v>
@@ -7226,16 +7310,16 @@
     </row>
     <row r="125" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A125" s="1">
-        <v>71519</v>
+        <v>71517</v>
       </c>
       <c r="B125" s="1">
         <v>1</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="F125" s="1" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
       <c r="N125" s="1">
         <v>5</v>
@@ -7249,19 +7333,16 @@
     </row>
     <row r="126" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A126" s="1">
-        <v>71520</v>
+        <v>71518</v>
       </c>
       <c r="B126" s="1">
         <v>1</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>307</v>
+        <v>313</v>
       </c>
       <c r="F126" s="1" t="s">
-        <v>308</v>
-      </c>
-      <c r="L126" s="1" t="s">
-        <v>55</v>
+        <v>314</v>
       </c>
       <c r="N126" s="1">
         <v>5</v>
@@ -7275,19 +7356,16 @@
     </row>
     <row r="127" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A127" s="1">
-        <v>71521</v>
+        <v>71519</v>
       </c>
       <c r="B127" s="1">
         <v>1</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="F127" s="1" t="s">
-        <v>310</v>
-      </c>
-      <c r="L127" s="1" t="s">
-        <v>55</v>
+        <v>315</v>
       </c>
       <c r="N127" s="1">
         <v>5</v>
@@ -7301,19 +7379,19 @@
     </row>
     <row r="128" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A128" s="1">
-        <v>71522</v>
+        <v>71520</v>
       </c>
       <c r="B128" s="1">
         <v>1</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="F128" s="1" t="s">
-        <v>312</v>
+        <v>317</v>
       </c>
       <c r="L128" s="1" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="N128" s="1">
         <v>5</v>
@@ -7327,19 +7405,19 @@
     </row>
     <row r="129" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A129" s="1">
-        <v>71523</v>
+        <v>71521</v>
       </c>
       <c r="B129" s="1">
         <v>1</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>313</v>
+        <v>318</v>
       </c>
       <c r="F129" s="1" t="s">
-        <v>314</v>
+        <v>319</v>
       </c>
       <c r="L129" s="1" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="N129" s="1">
         <v>5</v>
@@ -7353,22 +7431,19 @@
     </row>
     <row r="130" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A130" s="1">
-        <v>71524</v>
+        <v>71522</v>
       </c>
       <c r="B130" s="1">
         <v>1</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c r="F130" s="1" t="s">
-        <v>316</v>
-      </c>
-      <c r="K130" s="1">
-        <v>3</v>
+        <v>321</v>
       </c>
       <c r="L130" s="1" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="N130" s="1">
         <v>5</v>
@@ -7382,22 +7457,19 @@
     </row>
     <row r="131" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A131" s="1">
-        <v>71525</v>
+        <v>71523</v>
       </c>
       <c r="B131" s="1">
         <v>1</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>317</v>
+        <v>322</v>
       </c>
       <c r="F131" s="1" t="s">
-        <v>318</v>
-      </c>
-      <c r="K131" s="1">
-        <v>3</v>
+        <v>323</v>
       </c>
       <c r="L131" s="1" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="N131" s="1">
         <v>5</v>
@@ -7411,22 +7483,25 @@
     </row>
     <row r="132" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A132" s="1">
-        <v>71526</v>
+        <v>71524</v>
       </c>
       <c r="B132" s="1">
+        <v>1</v>
+      </c>
+      <c r="D132" s="1" t="s">
+        <v>324</v>
+      </c>
+      <c r="F132" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="K132" s="1">
         <v>3</v>
       </c>
-      <c r="F132" s="1" t="s">
-        <v>319</v>
-      </c>
-      <c r="K132" s="1">
-        <v>99</v>
-      </c>
       <c r="L132" s="1" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="N132" s="1">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Q132" s="1">
         <v>1</v>
@@ -7437,22 +7512,25 @@
     </row>
     <row r="133" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A133" s="1">
-        <v>71527</v>
+        <v>71525</v>
       </c>
       <c r="B133" s="1">
+        <v>1</v>
+      </c>
+      <c r="D133" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="F133" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="K133" s="1">
         <v>3</v>
       </c>
-      <c r="F133" s="1" t="s">
-        <v>310</v>
-      </c>
-      <c r="K133" s="1">
-        <v>99</v>
-      </c>
       <c r="L133" s="1" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="N133" s="1">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Q133" s="1">
         <v>1</v>
@@ -7463,19 +7541,19 @@
     </row>
     <row r="134" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A134" s="1">
-        <v>71528</v>
+        <v>71526</v>
       </c>
       <c r="B134" s="1">
         <v>3</v>
       </c>
       <c r="F134" s="1" t="s">
-        <v>312</v>
+        <v>328</v>
       </c>
       <c r="K134" s="1">
         <v>99</v>
       </c>
       <c r="L134" s="1" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="N134" s="1">
         <v>1</v>
@@ -7489,19 +7567,19 @@
     </row>
     <row r="135" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A135" s="1">
-        <v>71529</v>
+        <v>71527</v>
       </c>
       <c r="B135" s="1">
         <v>3</v>
       </c>
       <c r="F135" s="1" t="s">
-        <v>314</v>
+        <v>319</v>
       </c>
       <c r="K135" s="1">
         <v>99</v>
       </c>
       <c r="L135" s="1" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="N135" s="1">
         <v>1</v>
@@ -7515,19 +7593,19 @@
     </row>
     <row r="136" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A136" s="1">
-        <v>71530</v>
+        <v>71528</v>
       </c>
       <c r="B136" s="1">
         <v>3</v>
       </c>
       <c r="F136" s="1" t="s">
-        <v>316</v>
+        <v>321</v>
       </c>
       <c r="K136" s="1">
         <v>99</v>
       </c>
       <c r="L136" s="1" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="N136" s="1">
         <v>1</v>
@@ -7541,19 +7619,19 @@
     </row>
     <row r="137" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A137" s="1">
-        <v>71531</v>
+        <v>71529</v>
       </c>
       <c r="B137" s="1">
         <v>3</v>
       </c>
       <c r="F137" s="1" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="K137" s="1">
         <v>99</v>
       </c>
       <c r="L137" s="1" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="N137" s="1">
         <v>1</v>
@@ -7567,7 +7645,22 @@
     </row>
     <row r="138" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A138" s="1">
-        <v>71532</v>
+        <v>71530</v>
+      </c>
+      <c r="B138" s="1">
+        <v>3</v>
+      </c>
+      <c r="F138" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="K138" s="1">
+        <v>99</v>
+      </c>
+      <c r="L138" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="N138" s="1">
+        <v>1</v>
       </c>
       <c r="Q138" s="1">
         <v>1</v>
@@ -7578,7 +7671,22 @@
     </row>
     <row r="139" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A139" s="1">
-        <v>71533</v>
+        <v>71531</v>
+      </c>
+      <c r="B139" s="1">
+        <v>3</v>
+      </c>
+      <c r="F139" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="K139" s="1">
+        <v>99</v>
+      </c>
+      <c r="L139" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="N139" s="1">
+        <v>1</v>
       </c>
       <c r="Q139" s="1">
         <v>1</v>
@@ -7589,7 +7697,7 @@
     </row>
     <row r="140" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A140" s="1">
-        <v>71534</v>
+        <v>71532</v>
       </c>
       <c r="Q140" s="1">
         <v>1</v>
@@ -7600,7 +7708,7 @@
     </row>
     <row r="141" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A141" s="1">
-        <v>71535</v>
+        <v>71533</v>
       </c>
       <c r="Q141" s="1">
         <v>1</v>
@@ -7611,7 +7719,7 @@
     </row>
     <row r="142" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A142" s="1">
-        <v>71536</v>
+        <v>71534</v>
       </c>
       <c r="Q142" s="1">
         <v>1</v>
@@ -7622,7 +7730,7 @@
     </row>
     <row r="143" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A143" s="1">
-        <v>71537</v>
+        <v>71535</v>
       </c>
       <c r="Q143" s="1">
         <v>1</v>
@@ -7633,7 +7741,7 @@
     </row>
     <row r="144" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A144" s="1">
-        <v>71538</v>
+        <v>71536</v>
       </c>
       <c r="Q144" s="1">
         <v>1</v>
@@ -7644,7 +7752,7 @@
     </row>
     <row r="145" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A145" s="1">
-        <v>71539</v>
+        <v>71537</v>
       </c>
       <c r="Q145" s="1">
         <v>1</v>
@@ -7655,7 +7763,7 @@
     </row>
     <row r="146" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A146" s="1">
-        <v>71540</v>
+        <v>71538</v>
       </c>
       <c r="Q146" s="1">
         <v>1</v>
@@ -7666,7 +7774,7 @@
     </row>
     <row r="147" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A147" s="1">
-        <v>71541</v>
+        <v>71539</v>
       </c>
       <c r="Q147" s="1">
         <v>1</v>
@@ -7677,7 +7785,7 @@
     </row>
     <row r="148" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A148" s="1">
-        <v>71542</v>
+        <v>71540</v>
       </c>
       <c r="Q148" s="1">
         <v>1</v>
@@ -7688,7 +7796,7 @@
     </row>
     <row r="149" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A149" s="1">
-        <v>71543</v>
+        <v>71541</v>
       </c>
       <c r="Q149" s="1">
         <v>1</v>
@@ -7699,7 +7807,7 @@
     </row>
     <row r="150" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A150" s="1">
-        <v>71544</v>
+        <v>71542</v>
       </c>
       <c r="Q150" s="1">
         <v>1</v>
@@ -7710,7 +7818,7 @@
     </row>
     <row r="151" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A151" s="1">
-        <v>71545</v>
+        <v>71543</v>
       </c>
       <c r="Q151" s="1">
         <v>1</v>
@@ -7721,7 +7829,7 @@
     </row>
     <row r="152" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A152" s="1">
-        <v>71546</v>
+        <v>71544</v>
       </c>
       <c r="Q152" s="1">
         <v>1</v>
@@ -7732,7 +7840,7 @@
     </row>
     <row r="153" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A153" s="1">
-        <v>71547</v>
+        <v>71545</v>
       </c>
       <c r="Q153" s="1">
         <v>1</v>
@@ -7743,7 +7851,7 @@
     </row>
     <row r="154" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A154" s="1">
-        <v>71548</v>
+        <v>71546</v>
       </c>
       <c r="Q154" s="1">
         <v>1</v>
@@ -7754,7 +7862,7 @@
     </row>
     <row r="155" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A155" s="1">
-        <v>71549</v>
+        <v>71547</v>
       </c>
       <c r="Q155" s="1">
         <v>1</v>
@@ -7765,7 +7873,7 @@
     </row>
     <row r="156" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A156" s="1">
-        <v>71550</v>
+        <v>71548</v>
       </c>
       <c r="Q156" s="1">
         <v>1</v>
@@ -7776,7 +7884,7 @@
     </row>
     <row r="157" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A157" s="1">
-        <v>71551</v>
+        <v>71549</v>
       </c>
       <c r="Q157" s="1">
         <v>1</v>
@@ -7787,7 +7895,7 @@
     </row>
     <row r="158" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A158" s="1">
-        <v>71552</v>
+        <v>71550</v>
       </c>
       <c r="Q158" s="1">
         <v>1</v>
@@ -7798,7 +7906,7 @@
     </row>
     <row r="159" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A159" s="1">
-        <v>71553</v>
+        <v>71551</v>
       </c>
       <c r="Q159" s="1">
         <v>1</v>
@@ -7809,7 +7917,7 @@
     </row>
     <row r="160" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A160" s="1">
-        <v>71554</v>
+        <v>71552</v>
       </c>
       <c r="Q160" s="1">
         <v>1</v>
@@ -7820,7 +7928,7 @@
     </row>
     <row r="161" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A161" s="1">
-        <v>71555</v>
+        <v>71553</v>
       </c>
       <c r="Q161" s="1">
         <v>1</v>
@@ -7831,7 +7939,7 @@
     </row>
     <row r="162" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A162" s="1">
-        <v>71556</v>
+        <v>71554</v>
       </c>
       <c r="Q162" s="1">
         <v>1</v>
@@ -7842,7 +7950,7 @@
     </row>
     <row r="163" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A163" s="1">
-        <v>71557</v>
+        <v>71555</v>
       </c>
       <c r="Q163" s="1">
         <v>1</v>
@@ -7853,7 +7961,7 @@
     </row>
     <row r="164" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A164" s="1">
-        <v>71558</v>
+        <v>71556</v>
       </c>
       <c r="Q164" s="1">
         <v>1</v>
@@ -7864,7 +7972,7 @@
     </row>
     <row r="165" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A165" s="1">
-        <v>71559</v>
+        <v>71557</v>
       </c>
       <c r="Q165" s="1">
         <v>1</v>
@@ -7875,7 +7983,7 @@
     </row>
     <row r="166" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A166" s="1">
-        <v>71560</v>
+        <v>71558</v>
       </c>
       <c r="Q166" s="1">
         <v>1</v>
@@ -7886,7 +7994,7 @@
     </row>
     <row r="167" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A167" s="1">
-        <v>71561</v>
+        <v>71559</v>
       </c>
       <c r="Q167" s="1">
         <v>1</v>
@@ -7897,7 +8005,7 @@
     </row>
     <row r="168" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A168" s="1">
-        <v>71562</v>
+        <v>71560</v>
       </c>
       <c r="Q168" s="1">
         <v>1</v>
@@ -7908,7 +8016,7 @@
     </row>
     <row r="169" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A169" s="1">
-        <v>71563</v>
+        <v>71561</v>
       </c>
       <c r="Q169" s="1">
         <v>1</v>
@@ -7919,7 +8027,7 @@
     </row>
     <row r="170" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A170" s="1">
-        <v>71564</v>
+        <v>71562</v>
       </c>
       <c r="Q170" s="1">
         <v>1</v>
@@ -7930,7 +8038,7 @@
     </row>
     <row r="171" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A171" s="1">
-        <v>71565</v>
+        <v>71563</v>
       </c>
       <c r="Q171" s="1">
         <v>1</v>
@@ -7941,7 +8049,7 @@
     </row>
     <row r="172" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A172" s="1">
-        <v>71566</v>
+        <v>71564</v>
       </c>
       <c r="Q172" s="1">
         <v>1</v>
@@ -7952,7 +8060,7 @@
     </row>
     <row r="173" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A173" s="1">
-        <v>71567</v>
+        <v>71565</v>
       </c>
       <c r="Q173" s="1">
         <v>1</v>
@@ -7963,6 +8071,28 @@
     </row>
     <row r="174" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A174" s="1">
+        <v>71566</v>
+      </c>
+      <c r="Q174" s="1">
+        <v>1</v>
+      </c>
+      <c r="R174" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="175" spans="1:18" x14ac:dyDescent="0.15">
+      <c r="A175" s="1">
+        <v>71567</v>
+      </c>
+      <c r="Q175" s="1">
+        <v>1</v>
+      </c>
+      <c r="R175" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="176" spans="1:18" x14ac:dyDescent="0.15">
+      <c r="A176" s="1">
         <v>71568</v>
       </c>
     </row>
@@ -7970,7 +8100,7 @@
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A4:Q46">
     <sortCondition ref="B4:B46"/>
   </sortState>
-  <phoneticPr fontId="21" type="noConversion"/>
+  <phoneticPr fontId="22" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="200" verticalDpi="300"/>
   <legacyDrawing r:id="rId1"/>
@@ -7992,7 +8122,7 @@
         <v>9</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>321</v>
+        <v>330</v>
       </c>
       <c r="C1" s="5" t="s">
         <v>20</v>
@@ -8006,7 +8136,7 @@
         <v>-1</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>322</v>
+        <v>331</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.15">
@@ -8017,7 +8147,7 @@
         <v>1</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>323</v>
+        <v>332</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.15">
@@ -8028,7 +8158,7 @@
         <v>1</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>324</v>
+        <v>333</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.15">
@@ -8039,7 +8169,7 @@
         <v>1</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>325</v>
+        <v>334</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.15">
@@ -8050,7 +8180,7 @@
         <v>1</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>326</v>
+        <v>335</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.15">
@@ -8061,7 +8191,7 @@
         <v>2</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>327</v>
+        <v>336</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.15">
@@ -8072,7 +8202,7 @@
         <v>1</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>328</v>
+        <v>337</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.15">
@@ -8083,7 +8213,7 @@
         <v>1</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.15">
@@ -8094,7 +8224,7 @@
         <v>1</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>329</v>
+        <v>338</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.15">
@@ -8105,7 +8235,7 @@
         <v>1</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>330</v>
+        <v>339</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.15">
@@ -8116,7 +8246,7 @@
         <v>1</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>331</v>
+        <v>340</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.15">
@@ -8127,7 +8257,7 @@
         <v>1</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>332</v>
+        <v>341</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.15">
@@ -8146,7 +8276,7 @@
         <v>1</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>333</v>
+        <v>342</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.15">
@@ -8185,7 +8315,7 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="21" type="noConversion"/>
+  <phoneticPr fontId="22" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="200" verticalDpi="300"/>
 </worksheet>
@@ -8201,121 +8331,121 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A1" s="2" t="s">
-        <v>334</v>
+        <v>343</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A2" s="1" t="s">
-        <v>335</v>
+        <v>344</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A3" s="1" t="s">
-        <v>336</v>
+        <v>345</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A4" s="1" t="s">
-        <v>337</v>
+        <v>346</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A5" s="1" t="s">
-        <v>338</v>
+        <v>347</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A6" s="1" t="s">
-        <v>339</v>
+        <v>348</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A7" s="1" t="s">
-        <v>340</v>
+        <v>349</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A8" s="1" t="s">
-        <v>341</v>
+        <v>350</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A9" s="1" t="s">
-        <v>342</v>
+        <v>351</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A10" s="1" t="s">
-        <v>343</v>
+        <v>352</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A11" s="1" t="s">
-        <v>344</v>
+        <v>353</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A12" s="1" t="s">
-        <v>345</v>
+        <v>354</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A13" s="1" t="s">
-        <v>346</v>
+        <v>355</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A14" s="1" t="s">
-        <v>347</v>
+        <v>356</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A15" s="1" t="s">
-        <v>348</v>
+        <v>357</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A16" s="1" t="s">
-        <v>349</v>
+        <v>358</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A17" s="1" t="s">
-        <v>350</v>
+        <v>359</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A18" s="1" t="s">
-        <v>351</v>
+        <v>360</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A19" s="1" t="s">
-        <v>352</v>
+        <v>361</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A20" s="1" t="s">
-        <v>353</v>
+        <v>362</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A21" s="1" t="s">
-        <v>354</v>
+        <v>363</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A22" s="1" t="s">
-        <v>355</v>
+        <v>364</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A23" s="1" t="s">
-        <v>356</v>
+        <v>365</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="21" type="noConversion"/>
+  <phoneticPr fontId="22" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="200" verticalDpi="300"/>
 </worksheet>

--- a/Luban/Excel/CombatBuff.xlsx
+++ b/Luban/Excel/CombatBuff.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\Return0\Luban\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6320B18-2E4F-4E3C-BCDF-2FA2C934C69C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86FC2923-4DC4-4A1A-AA5F-10494DB9EF42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
